--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Indigo Construction\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\DEN Camera System\Indigo Construction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{10A543A2-B8CB-49CB-B2C1-630C223C249E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B8724C-6128-400D-9554-9432B2C1540F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="23295" windowHeight="13380" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\DEN Camera System\Indigo Construction\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Indigo Construction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B8724C-6128-400D-9554-9432B2C1540F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3F74E41-CA82-452D-BEF7-359593B71613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -499,7 +499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="B1:K5929"/>
+  <dimension ref="A1:K5929"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -514,39 +514,39 @@
     <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>18</v>
       </c>
@@ -575,14 +575,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H3" s="2"/>
       <c r="I3" s="1"/>
       <c r="K3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>18</v>
       </c>
@@ -611,7 +611,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>18</v>
       </c>
@@ -640,7 +640,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>18</v>
       </c>
@@ -669,7 +669,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>18</v>
       </c>
@@ -698,7 +698,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>18</v>
       </c>
@@ -727,7 +727,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>18</v>
       </c>
@@ -756,7 +756,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>18</v>
       </c>
@@ -785,7 +785,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>18</v>
       </c>
@@ -814,7 +814,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>18</v>
       </c>
@@ -843,7 +843,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>18</v>
       </c>
@@ -872,7 +872,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>18</v>
       </c>
@@ -901,14 +901,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H15" s="2"/>
       <c r="I15" s="1"/>
       <c r="K15" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>18</v>
       </c>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Indigo Construction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3F74E41-CA82-452D-BEF7-359593B71613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F250BD00-51FA-4D6B-8F63-6833B3A8E6EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -499,7 +499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K5929"/>
+  <dimension ref="B1:K5929"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -514,39 +514,39 @@
     <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>18</v>
       </c>
@@ -575,14 +575,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H3" s="2"/>
       <c r="I3" s="1"/>
       <c r="K3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>18</v>
       </c>
@@ -611,7 +611,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>18</v>
       </c>
@@ -640,7 +640,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>18</v>
       </c>
@@ -669,7 +669,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>18</v>
       </c>
@@ -698,7 +698,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>18</v>
       </c>
@@ -727,7 +727,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>18</v>
       </c>
@@ -756,7 +756,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>18</v>
       </c>
@@ -785,7 +785,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>18</v>
       </c>
@@ -814,7 +814,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>18</v>
       </c>
@@ -843,7 +843,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>18</v>
       </c>
@@ -872,7 +872,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>18</v>
       </c>
@@ -901,14 +901,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H15" s="2"/>
       <c r="I15" s="1"/>
       <c r="K15" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>18</v>
       </c>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Indigo Construction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F250BD00-51FA-4D6B-8F63-6833B3A8E6EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A9D3254-B5A6-4E26-A3CD-84F4D4181584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="31">
   <si>
     <t>Company Name</t>
   </si>
@@ -126,6 +126,12 @@
   </si>
   <si>
     <t>Oscar Reyna</t>
+  </si>
+  <si>
+    <t>Space Management for Commercial Vehicles</t>
+  </si>
+  <si>
+    <t>UNKNOWN</t>
   </si>
 </sst>
 </file>
@@ -1445,48 +1451,301 @@
       </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H36" s="2"/>
-      <c r="I36" s="1"/>
+      <c r="B36" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36">
+        <v>5162</v>
+      </c>
+      <c r="D36" t="s">
+        <v>19</v>
+      </c>
+      <c r="F36" t="s">
+        <v>29</v>
+      </c>
+      <c r="G36" t="s">
+        <v>13</v>
+      </c>
+      <c r="H36" s="2">
+        <v>0</v>
+      </c>
+      <c r="I36" s="1">
+        <v>46118.764467592591</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H37" s="2"/>
-      <c r="I37" s="1"/>
+      <c r="B37" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37">
+        <v>5166</v>
+      </c>
+      <c r="D37" t="s">
+        <v>20</v>
+      </c>
+      <c r="F37" t="s">
+        <v>29</v>
+      </c>
+      <c r="G37" t="s">
+        <v>13</v>
+      </c>
+      <c r="H37" s="2">
+        <v>0</v>
+      </c>
+      <c r="I37" s="1">
+        <v>46118.765162037038</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H38" s="2"/>
-      <c r="I38" s="1"/>
+      <c r="B38" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38">
+        <v>5168</v>
+      </c>
+      <c r="D38" t="s">
+        <v>21</v>
+      </c>
+      <c r="F38" t="s">
+        <v>29</v>
+      </c>
+      <c r="G38" t="s">
+        <v>13</v>
+      </c>
+      <c r="H38" s="2">
+        <v>0</v>
+      </c>
+      <c r="I38" s="1">
+        <v>46118.765856481485</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H39" s="2"/>
-      <c r="I39" s="1"/>
+      <c r="B39" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39">
+        <v>5163</v>
+      </c>
+      <c r="D39" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" t="s">
+        <v>29</v>
+      </c>
+      <c r="G39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H39" s="2">
+        <v>0</v>
+      </c>
+      <c r="I39" s="1">
+        <v>46118.765856481485</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H40" s="2"/>
-      <c r="I40" s="1"/>
+      <c r="B40" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40">
+        <v>5159</v>
+      </c>
+      <c r="D40" t="s">
+        <v>23</v>
+      </c>
+      <c r="F40" t="s">
+        <v>29</v>
+      </c>
+      <c r="G40" t="s">
+        <v>13</v>
+      </c>
+      <c r="H40" s="2">
+        <v>0</v>
+      </c>
+      <c r="I40" s="1">
+        <v>46118.766550925924</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H41" s="2"/>
-      <c r="I41" s="1"/>
+      <c r="B41" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41">
+        <v>5165</v>
+      </c>
+      <c r="D41" t="s">
+        <v>24</v>
+      </c>
+      <c r="F41" t="s">
+        <v>29</v>
+      </c>
+      <c r="G41" t="s">
+        <v>13</v>
+      </c>
+      <c r="H41" s="2">
+        <v>0</v>
+      </c>
+      <c r="I41" s="1">
+        <v>46118.766550925924</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H42" s="2"/>
-      <c r="I42" s="1"/>
+      <c r="B42" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42">
+        <v>5160</v>
+      </c>
+      <c r="D42" t="s">
+        <v>25</v>
+      </c>
+      <c r="F42" t="s">
+        <v>29</v>
+      </c>
+      <c r="G42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H42" s="2">
+        <v>0</v>
+      </c>
+      <c r="I42" s="1">
+        <v>46118.767245370371</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H43" s="2"/>
-      <c r="I43" s="1"/>
+      <c r="B43" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43">
+        <v>5161</v>
+      </c>
+      <c r="D43" t="s">
+        <v>26</v>
+      </c>
+      <c r="F43" t="s">
+        <v>29</v>
+      </c>
+      <c r="G43" t="s">
+        <v>13</v>
+      </c>
+      <c r="H43" s="2">
+        <v>0</v>
+      </c>
+      <c r="I43" s="1">
+        <v>46118.767245370371</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H44" s="2"/>
-      <c r="I44" s="1"/>
+      <c r="B44" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44">
+        <v>5167</v>
+      </c>
+      <c r="D44" t="s">
+        <v>27</v>
+      </c>
+      <c r="F44" t="s">
+        <v>29</v>
+      </c>
+      <c r="G44" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44" s="2">
+        <v>0</v>
+      </c>
+      <c r="I44" s="1">
+        <v>46118.767939814818</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H45" s="2"/>
-      <c r="I45" s="1"/>
+      <c r="B45" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45">
+        <v>5164</v>
+      </c>
+      <c r="D45" t="s">
+        <v>28</v>
+      </c>
+      <c r="F45" t="s">
+        <v>29</v>
+      </c>
+      <c r="G45" t="s">
+        <v>30</v>
+      </c>
+      <c r="H45" s="2">
+        <v>0</v>
+      </c>
+      <c r="I45" s="1">
+        <v>46118.768634259257</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H46" s="2"/>
       <c r="I46" s="1"/>
+      <c r="K46" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H47" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Indigo Construction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A9D3254-B5A6-4E26-A3CD-84F4D4181584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{796C4015-D5C2-4D7D-BCCD-C979BED16018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="31">
   <si>
     <t>Company Name</t>
   </si>
@@ -1348,10 +1348,10 @@
         <v>14</v>
       </c>
       <c r="G32" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H32" s="2">
-        <v>0</v>
+        <v>1.019675925925926E-2</v>
       </c>
       <c r="I32" s="1">
         <v>46083.757291666669</v>
@@ -1364,32 +1364,10 @@
       </c>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B33" t="s">
-        <v>18</v>
-      </c>
-      <c r="C33">
-        <v>5161</v>
-      </c>
-      <c r="D33" t="s">
-        <v>26</v>
-      </c>
-      <c r="F33" t="s">
-        <v>14</v>
-      </c>
-      <c r="G33" t="s">
-        <v>13</v>
-      </c>
-      <c r="H33" s="2">
-        <v>0</v>
-      </c>
-      <c r="I33" s="1">
-        <v>46083.757986111108</v>
-      </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
+      <c r="H33" s="2"/>
+      <c r="I33" s="1"/>
       <c r="K33" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
@@ -1397,10 +1375,10 @@
         <v>18</v>
       </c>
       <c r="C34">
-        <v>5167</v>
+        <v>5161</v>
       </c>
       <c r="D34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F34" t="s">
         <v>14</v>
@@ -1412,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="1">
-        <v>46083.758680555555</v>
+        <v>46083.757986111108</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -1426,10 +1404,10 @@
         <v>18</v>
       </c>
       <c r="C35">
-        <v>5164</v>
+        <v>5167</v>
       </c>
       <c r="D35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F35" t="s">
         <v>14</v>
@@ -1455,13 +1433,13 @@
         <v>18</v>
       </c>
       <c r="C36">
-        <v>5162</v>
+        <v>5164</v>
       </c>
       <c r="D36" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F36" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="G36" t="s">
         <v>13</v>
@@ -1470,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="I36" s="1">
-        <v>46118.764467592591</v>
+        <v>46083.758680555555</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -1484,10 +1462,10 @@
         <v>18</v>
       </c>
       <c r="C37">
-        <v>5166</v>
+        <v>5162</v>
       </c>
       <c r="D37" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F37" t="s">
         <v>29</v>
@@ -1499,7 +1477,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="1">
-        <v>46118.765162037038</v>
+        <v>46118.764467592591</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -1513,10 +1491,10 @@
         <v>18</v>
       </c>
       <c r="C38">
-        <v>5168</v>
+        <v>5166</v>
       </c>
       <c r="D38" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F38" t="s">
         <v>29</v>
@@ -1528,7 +1506,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="1">
-        <v>46118.765856481485</v>
+        <v>46118.765162037038</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -1542,10 +1520,10 @@
         <v>18</v>
       </c>
       <c r="C39">
-        <v>5163</v>
+        <v>5168</v>
       </c>
       <c r="D39" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F39" t="s">
         <v>29</v>
@@ -1571,10 +1549,10 @@
         <v>18</v>
       </c>
       <c r="C40">
-        <v>5159</v>
+        <v>5163</v>
       </c>
       <c r="D40" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F40" t="s">
         <v>29</v>
@@ -1586,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="1">
-        <v>46118.766550925924</v>
+        <v>46118.765856481485</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -1600,10 +1578,10 @@
         <v>18</v>
       </c>
       <c r="C41">
-        <v>5165</v>
+        <v>5159</v>
       </c>
       <c r="D41" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F41" t="s">
         <v>29</v>
@@ -1629,10 +1607,10 @@
         <v>18</v>
       </c>
       <c r="C42">
-        <v>5160</v>
+        <v>5165</v>
       </c>
       <c r="D42" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F42" t="s">
         <v>29</v>
@@ -1644,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="1">
-        <v>46118.767245370371</v>
+        <v>46118.766550925924</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -1658,10 +1636,10 @@
         <v>18</v>
       </c>
       <c r="C43">
-        <v>5161</v>
+        <v>5160</v>
       </c>
       <c r="D43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F43" t="s">
         <v>29</v>
@@ -1687,10 +1665,10 @@
         <v>18</v>
       </c>
       <c r="C44">
-        <v>5167</v>
+        <v>5161</v>
       </c>
       <c r="D44" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F44" t="s">
         <v>29</v>
@@ -1702,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="I44" s="1">
-        <v>46118.767939814818</v>
+        <v>46118.767245370371</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -1716,22 +1694,22 @@
         <v>18</v>
       </c>
       <c r="C45">
-        <v>5164</v>
+        <v>5167</v>
       </c>
       <c r="D45" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F45" t="s">
         <v>29</v>
       </c>
       <c r="G45" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="H45" s="2">
         <v>0</v>
       </c>
       <c r="I45" s="1">
-        <v>46118.768634259257</v>
+        <v>46118.767939814818</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -1741,15 +1719,40 @@
       </c>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H46" s="2"/>
-      <c r="I46" s="1"/>
+      <c r="B46" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46">
+        <v>5164</v>
+      </c>
+      <c r="D46" t="s">
+        <v>28</v>
+      </c>
+      <c r="F46" t="s">
+        <v>29</v>
+      </c>
+      <c r="G46" t="s">
+        <v>30</v>
+      </c>
+      <c r="H46" s="2">
+        <v>0</v>
+      </c>
+      <c r="I46" s="1">
+        <v>46118.768634259257</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
       <c r="K46" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H47" s="2"/>
       <c r="I47" s="1"/>
+      <c r="K47" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H48" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Indigo Construction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{796C4015-D5C2-4D7D-BCCD-C979BED16018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12124B00-833F-4236-80D9-3D48E7B8F984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2760" yWindow="810" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Indigo Construction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12124B00-833F-4236-80D9-3D48E7B8F984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1EF2278-66F5-420C-AA84-270ADBA7CE6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="810" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="32">
   <si>
     <t>Company Name</t>
   </si>
@@ -132,6 +132,9 @@
   </si>
   <si>
     <t>UNKNOWN</t>
+  </si>
+  <si>
+    <t>Rules for Safe Driving</t>
   </si>
 </sst>
 </file>
@@ -1755,70 +1758,326 @@
       </c>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H48" s="2"/>
-      <c r="I48" s="1"/>
-    </row>
-    <row r="49" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48">
+        <v>5162</v>
+      </c>
+      <c r="D48" t="s">
+        <v>19</v>
+      </c>
+      <c r="F48" t="s">
+        <v>31</v>
+      </c>
+      <c r="G48" t="s">
+        <v>12</v>
+      </c>
+      <c r="H48" s="2">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="I48" s="1">
+        <v>46146.672453703701</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H49" s="2"/>
       <c r="I49" s="1"/>
-    </row>
-    <row r="50" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H50" s="2"/>
-      <c r="I50" s="1"/>
-    </row>
-    <row r="51" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K49" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50">
+        <v>5166</v>
+      </c>
+      <c r="D50" t="s">
+        <v>20</v>
+      </c>
+      <c r="F50" t="s">
+        <v>31</v>
+      </c>
+      <c r="G50" t="s">
+        <v>30</v>
+      </c>
+      <c r="H50" s="2">
+        <v>0</v>
+      </c>
+      <c r="I50" s="1">
+        <v>46146.673148148147</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H51" s="2"/>
       <c r="I51" s="1"/>
-    </row>
-    <row r="52" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H52" s="2"/>
-      <c r="I52" s="1"/>
-    </row>
-    <row r="53" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H53" s="2"/>
-      <c r="I53" s="1"/>
-    </row>
-    <row r="54" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H54" s="2"/>
-      <c r="I54" s="1"/>
-    </row>
-    <row r="55" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H55" s="2"/>
-      <c r="I55" s="1"/>
-    </row>
-    <row r="56" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H56" s="2"/>
-      <c r="I56" s="1"/>
-    </row>
-    <row r="57" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H57" s="2"/>
-      <c r="I57" s="1"/>
-    </row>
-    <row r="58" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H58" s="2"/>
-      <c r="I58" s="1"/>
-    </row>
-    <row r="59" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H59" s="2"/>
-      <c r="I59" s="1"/>
-    </row>
-    <row r="60" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K51" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52">
+        <v>5168</v>
+      </c>
+      <c r="D52" t="s">
+        <v>21</v>
+      </c>
+      <c r="F52" t="s">
+        <v>31</v>
+      </c>
+      <c r="G52" t="s">
+        <v>13</v>
+      </c>
+      <c r="H52" s="2">
+        <v>0</v>
+      </c>
+      <c r="I52" s="1">
+        <v>46146.673842592594</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53">
+        <v>5163</v>
+      </c>
+      <c r="D53" t="s">
+        <v>22</v>
+      </c>
+      <c r="F53" t="s">
+        <v>31</v>
+      </c>
+      <c r="G53" t="s">
+        <v>13</v>
+      </c>
+      <c r="H53" s="2">
+        <v>0</v>
+      </c>
+      <c r="I53" s="1">
+        <v>46146.673842592594</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54">
+        <v>5159</v>
+      </c>
+      <c r="D54" t="s">
+        <v>23</v>
+      </c>
+      <c r="F54" t="s">
+        <v>31</v>
+      </c>
+      <c r="G54" t="s">
+        <v>13</v>
+      </c>
+      <c r="H54" s="2">
+        <v>0</v>
+      </c>
+      <c r="I54" s="1">
+        <v>46146.674537037034</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55">
+        <v>5165</v>
+      </c>
+      <c r="D55" t="s">
+        <v>24</v>
+      </c>
+      <c r="F55" t="s">
+        <v>31</v>
+      </c>
+      <c r="G55" t="s">
+        <v>13</v>
+      </c>
+      <c r="H55" s="2">
+        <v>0</v>
+      </c>
+      <c r="I55" s="1">
+        <v>46146.674537037034</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56">
+        <v>5160</v>
+      </c>
+      <c r="D56" t="s">
+        <v>25</v>
+      </c>
+      <c r="F56" t="s">
+        <v>31</v>
+      </c>
+      <c r="G56" t="s">
+        <v>13</v>
+      </c>
+      <c r="H56" s="2">
+        <v>0</v>
+      </c>
+      <c r="I56" s="1">
+        <v>46146.67523148148</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>18</v>
+      </c>
+      <c r="C57">
+        <v>5161</v>
+      </c>
+      <c r="D57" t="s">
+        <v>26</v>
+      </c>
+      <c r="F57" t="s">
+        <v>31</v>
+      </c>
+      <c r="G57" t="s">
+        <v>13</v>
+      </c>
+      <c r="H57" s="2">
+        <v>0</v>
+      </c>
+      <c r="I57" s="1">
+        <v>46146.675925925927</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
+        <v>18</v>
+      </c>
+      <c r="C58">
+        <v>5167</v>
+      </c>
+      <c r="D58" t="s">
+        <v>27</v>
+      </c>
+      <c r="F58" t="s">
+        <v>31</v>
+      </c>
+      <c r="G58" t="s">
+        <v>13</v>
+      </c>
+      <c r="H58" s="2">
+        <v>0</v>
+      </c>
+      <c r="I58" s="1">
+        <v>46146.676620370374</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59">
+        <v>5164</v>
+      </c>
+      <c r="D59" t="s">
+        <v>28</v>
+      </c>
+      <c r="F59" t="s">
+        <v>31</v>
+      </c>
+      <c r="G59" t="s">
+        <v>13</v>
+      </c>
+      <c r="H59" s="2">
+        <v>0</v>
+      </c>
+      <c r="I59" s="1">
+        <v>46146.676620370374</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H60" s="2"/>
       <c r="I60" s="1"/>
     </row>
-    <row r="61" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H61" s="2"/>
       <c r="I61" s="1"/>
     </row>
-    <row r="62" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H62" s="2"/>
       <c r="I62" s="1"/>
     </row>
-    <row r="63" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H63" s="2"/>
       <c r="I63" s="1"/>
     </row>
-    <row r="64" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H64" s="2"/>
       <c r="I64" s="1"/>
     </row>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Indigo Construction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1EF2278-66F5-420C-AA84-270ADBA7CE6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{769C25BE-7CD7-4571-BA83-07ED500806C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>

--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Indigo Construction- TS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Indigo-Construction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1903C5F2-95F8-4176-9476-E9259083AA41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62E9AD92-38BA-4263-84FE-C04FC4F0B72C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27390" yWindow="255" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2204,7 +2204,7 @@
         <v>46176.459953703707</v>
       </c>
       <c r="J64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K64" t="s">
         <v>11</v>
@@ -2271,7 +2271,7 @@
         <v>46176.460648148146</v>
       </c>
       <c r="J67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K67" t="s">
         <v>11</v>
@@ -2300,7 +2300,7 @@
         <v>46176.461342592593</v>
       </c>
       <c r="J68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K68" t="s">
         <v>11</v>
@@ -2329,7 +2329,7 @@
         <v>46176.461342592593</v>
       </c>
       <c r="J69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K69" t="s">
         <v>11</v>
@@ -2396,7 +2396,7 @@
         <v>46176.462037037039</v>
       </c>
       <c r="J72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K72" t="s">
         <v>11</v>
@@ -2425,7 +2425,7 @@
         <v>46176.462731481479</v>
       </c>
       <c r="J73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K73" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Indigo-Construction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AE6B05E8-2FC9-445B-AFBC-F58DB7616769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{36A2F0FA-12AF-4B7C-8AEE-06D28F59C827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="36">
   <si>
     <t>Company Name</t>
   </si>
@@ -108,6 +108,9 @@
   </si>
   <si>
     <t>Camera Event Management Orientation for Drivers</t>
+  </si>
+  <si>
+    <t>Big Wins Through Behavior Change</t>
   </si>
   <si>
     <t>Indigo Construction</t>
@@ -517,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M6919"/>
+  <dimension ref="D1:M7172"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -566,13 +569,13 @@
     </row>
     <row r="2" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2">
         <v>5162</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>19</v>
@@ -604,13 +607,13 @@
     </row>
     <row r="4" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4">
         <v>5166</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>19</v>
@@ -633,13 +636,13 @@
     </row>
     <row r="5" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5">
         <v>5168</v>
       </c>
       <c r="F5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>19</v>
@@ -662,13 +665,13 @@
     </row>
     <row r="6" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6">
         <v>5163</v>
       </c>
       <c r="F6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>19</v>
@@ -691,13 +694,13 @@
     </row>
     <row r="7" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7">
         <v>5159</v>
       </c>
       <c r="F7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>19</v>
@@ -720,13 +723,13 @@
     </row>
     <row r="8" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E8">
         <v>5165</v>
       </c>
       <c r="F8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>19</v>
@@ -749,13 +752,13 @@
     </row>
     <row r="9" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E9">
         <v>5160</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>19</v>
@@ -778,13 +781,13 @@
     </row>
     <row r="10" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E10">
         <v>5161</v>
       </c>
       <c r="F10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>19</v>
@@ -807,13 +810,13 @@
     </row>
     <row r="11" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E11">
         <v>5167</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>19</v>
@@ -836,13 +839,13 @@
     </row>
     <row r="12" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E12">
         <v>5164</v>
       </c>
       <c r="F12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>19</v>
@@ -865,13 +868,13 @@
     </row>
     <row r="13" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E13">
         <v>5162</v>
       </c>
       <c r="F13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>22</v>
@@ -894,13 +897,13 @@
     </row>
     <row r="14" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E14">
         <v>5166</v>
       </c>
       <c r="F14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>22</v>
@@ -932,13 +935,13 @@
     </row>
     <row r="16" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E16">
         <v>5168</v>
       </c>
       <c r="F16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>22</v>
@@ -961,13 +964,13 @@
     </row>
     <row r="17" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E17">
         <v>5163</v>
       </c>
       <c r="F17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>22</v>
@@ -990,13 +993,13 @@
     </row>
     <row r="18" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E18">
         <v>5159</v>
       </c>
       <c r="F18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>22</v>
@@ -1019,13 +1022,13 @@
     </row>
     <row r="19" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E19">
         <v>5165</v>
       </c>
       <c r="F19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>22</v>
@@ -1048,13 +1051,13 @@
     </row>
     <row r="20" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E20">
         <v>5160</v>
       </c>
       <c r="F20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>22</v>
@@ -1086,13 +1089,13 @@
     </row>
     <row r="22" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E22">
         <v>5161</v>
       </c>
       <c r="F22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>22</v>
@@ -1115,13 +1118,13 @@
     </row>
     <row r="23" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E23">
         <v>5167</v>
       </c>
       <c r="F23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>22</v>
@@ -1144,13 +1147,13 @@
     </row>
     <row r="24" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E24">
         <v>5164</v>
       </c>
       <c r="F24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>22</v>
@@ -1182,13 +1185,13 @@
     </row>
     <row r="26" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E26">
         <v>5162</v>
       </c>
       <c r="F26" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>17</v>
@@ -1211,13 +1214,13 @@
     </row>
     <row r="27" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E27">
         <v>5166</v>
       </c>
       <c r="F27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>17</v>
@@ -1240,13 +1243,13 @@
     </row>
     <row r="28" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D28" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E28">
         <v>5168</v>
       </c>
       <c r="F28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>17</v>
@@ -1269,13 +1272,13 @@
     </row>
     <row r="29" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E29">
         <v>5163</v>
       </c>
       <c r="F29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>17</v>
@@ -1298,13 +1301,13 @@
     </row>
     <row r="30" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E30">
         <v>5159</v>
       </c>
       <c r="F30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>17</v>
@@ -1327,13 +1330,13 @@
     </row>
     <row r="31" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D31" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E31">
         <v>5165</v>
       </c>
       <c r="F31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>17</v>
@@ -1356,13 +1359,13 @@
     </row>
     <row r="32" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D32" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E32">
         <v>5160</v>
       </c>
       <c r="F32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>17</v>
@@ -1394,13 +1397,13 @@
     </row>
     <row r="34" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D34" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E34">
         <v>5161</v>
       </c>
       <c r="F34" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>17</v>
@@ -1423,13 +1426,13 @@
     </row>
     <row r="35" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D35" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E35">
         <v>5167</v>
       </c>
       <c r="F35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>17</v>
@@ -1452,13 +1455,13 @@
     </row>
     <row r="36" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D36" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E36">
         <v>5164</v>
       </c>
       <c r="F36" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>17</v>
@@ -1481,13 +1484,13 @@
     </row>
     <row r="37" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D37" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E37">
         <v>5162</v>
       </c>
       <c r="F37" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>20</v>
@@ -1510,13 +1513,13 @@
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D38" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E38">
         <v>5166</v>
       </c>
       <c r="F38" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>20</v>
@@ -1539,13 +1542,13 @@
     </row>
     <row r="39" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D39" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E39">
         <v>5168</v>
       </c>
       <c r="F39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>20</v>
@@ -1568,13 +1571,13 @@
     </row>
     <row r="40" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D40" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E40">
         <v>5163</v>
       </c>
       <c r="F40" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>20</v>
@@ -1597,13 +1600,13 @@
     </row>
     <row r="41" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D41" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E41">
         <v>5159</v>
       </c>
       <c r="F41" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>20</v>
@@ -1626,13 +1629,13 @@
     </row>
     <row r="42" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D42" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E42">
         <v>5165</v>
       </c>
       <c r="F42" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>20</v>
@@ -1655,13 +1658,13 @@
     </row>
     <row r="43" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D43" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E43">
         <v>5160</v>
       </c>
       <c r="F43" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>20</v>
@@ -1684,13 +1687,13 @@
     </row>
     <row r="44" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D44" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E44">
         <v>5161</v>
       </c>
       <c r="F44" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>20</v>
@@ -1713,13 +1716,13 @@
     </row>
     <row r="45" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D45" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E45">
         <v>5167</v>
       </c>
       <c r="F45" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>20</v>
@@ -1742,13 +1745,13 @@
     </row>
     <row r="46" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D46" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E46">
         <v>5164</v>
       </c>
       <c r="F46" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>20</v>
@@ -1780,13 +1783,13 @@
     </row>
     <row r="48" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D48" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E48">
         <v>5162</v>
       </c>
       <c r="F48" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>16</v>
@@ -1809,13 +1812,13 @@
     </row>
     <row r="49" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D49" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E49">
         <v>5166</v>
       </c>
       <c r="F49" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>16</v>
@@ -1847,13 +1850,13 @@
     </row>
     <row r="51" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D51" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E51">
         <v>5168</v>
       </c>
       <c r="F51" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>16</v>
@@ -1876,13 +1879,13 @@
     </row>
     <row r="52" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D52" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E52">
         <v>5163</v>
       </c>
       <c r="F52" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>16</v>
@@ -1905,13 +1908,13 @@
     </row>
     <row r="53" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D53" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E53">
         <v>5159</v>
       </c>
       <c r="F53" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>16</v>
@@ -1934,13 +1937,13 @@
     </row>
     <row r="54" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D54" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E54">
         <v>5165</v>
       </c>
       <c r="F54" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>16</v>
@@ -1963,13 +1966,13 @@
     </row>
     <row r="55" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D55" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E55">
         <v>5160</v>
       </c>
       <c r="F55" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>16</v>
@@ -1992,13 +1995,13 @@
     </row>
     <row r="56" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D56" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E56">
         <v>5161</v>
       </c>
       <c r="F56" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>16</v>
@@ -2021,13 +2024,13 @@
     </row>
     <row r="57" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D57" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E57">
         <v>5167</v>
       </c>
       <c r="F57" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>16</v>
@@ -2059,13 +2062,13 @@
     </row>
     <row r="59" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D59" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E59">
         <v>5164</v>
       </c>
       <c r="F59" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>16</v>
@@ -2088,13 +2091,13 @@
     </row>
     <row r="60" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D60" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E60">
         <v>5668</v>
       </c>
       <c r="F60" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>15</v>
@@ -2117,13 +2120,13 @@
     </row>
     <row r="61" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D61" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E61">
         <v>5167</v>
       </c>
       <c r="F61" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>15</v>
@@ -2146,13 +2149,13 @@
     </row>
     <row r="62" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D62" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E62">
         <v>5168</v>
       </c>
       <c r="F62" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>21</v>
@@ -2175,13 +2178,13 @@
     </row>
     <row r="63" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D63" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E63">
         <v>5162</v>
       </c>
       <c r="F63" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>21</v>
@@ -2204,13 +2207,13 @@
     </row>
     <row r="64" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D64" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E64">
         <v>5166</v>
       </c>
       <c r="F64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>21</v>
@@ -2242,13 +2245,13 @@
     </row>
     <row r="66" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D66" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E66">
         <v>5163</v>
       </c>
       <c r="F66" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>21</v>
@@ -2271,13 +2274,13 @@
     </row>
     <row r="67" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D67" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E67">
         <v>5159</v>
       </c>
       <c r="F67" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>21</v>
@@ -2300,13 +2303,13 @@
     </row>
     <row r="68" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D68" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E68">
         <v>5165</v>
       </c>
       <c r="F68" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>21</v>
@@ -2329,22 +2332,22 @@
     </row>
     <row r="69" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D69" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E69">
         <v>5160</v>
       </c>
       <c r="F69" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J69" s="2">
-        <v>0</v>
+        <v>1.1643518518518518E-2</v>
       </c>
       <c r="K69" s="1">
         <v>46176.462037037039</v>
@@ -2357,35 +2360,55 @@
       </c>
     </row>
     <row r="70" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H70" s="2"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="2"/>
-      <c r="K70" s="1"/>
+      <c r="D70" t="s">
+        <v>24</v>
+      </c>
+      <c r="E70">
+        <v>5161</v>
+      </c>
+      <c r="F70" t="s">
+        <v>32</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J70" s="2">
+        <v>0</v>
+      </c>
+      <c r="K70" s="1">
+        <v>46176.462037037039</v>
+      </c>
+      <c r="L70">
+        <v>3</v>
+      </c>
       <c r="M70" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="71" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D71" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E71">
-        <v>5161</v>
+        <v>5164</v>
       </c>
       <c r="F71" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J71" s="2">
-        <v>0</v>
+        <v>1.8518518518518518E-4</v>
       </c>
       <c r="K71" s="1">
-        <v>46176.462037037039</v>
+        <v>46176.462731481479</v>
       </c>
       <c r="L71">
         <v>3</v>
@@ -2395,41 +2418,41 @@
       </c>
     </row>
     <row r="72" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D72" t="s">
+      <c r="H72" s="2"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="2"/>
+      <c r="K72" s="1"/>
+      <c r="M72" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="73" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D73" t="s">
+        <v>24</v>
+      </c>
+      <c r="E73">
+        <v>5668</v>
+      </c>
+      <c r="F73" t="s">
+        <v>35</v>
+      </c>
+      <c r="H73" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E72">
-        <v>5164</v>
-      </c>
-      <c r="F72" t="s">
-        <v>33</v>
-      </c>
-      <c r="H72" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I72" s="1" t="s">
+      <c r="I73" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J72" s="2">
-        <v>1.8518518518518518E-4</v>
-      </c>
-      <c r="K72" s="1">
-        <v>46176.462731481479</v>
-      </c>
-      <c r="L72">
-        <v>3</v>
-      </c>
-      <c r="M72" t="s">
+      <c r="J73" s="2">
+        <v>9.0277777777777769E-3</v>
+      </c>
+      <c r="K73" s="1">
+        <v>46209.043287037035</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="73" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H73" s="2"/>
-      <c r="I73" s="1"/>
-      <c r="J73" s="2"/>
-      <c r="K73" s="1"/>
-      <c r="M73" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="74" spans="4:13" x14ac:dyDescent="0.3">
@@ -2437,6 +2460,9 @@
       <c r="I74" s="1"/>
       <c r="J74" s="2"/>
       <c r="K74" s="1"/>
+      <c r="M74" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="75" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H75" s="2"/>
@@ -6749,6 +6775,7 @@
     <row r="794" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H794" s="2"/>
       <c r="I794" s="1"/>
+      <c r="J794" s="2"/>
       <c r="K794" s="1"/>
     </row>
     <row r="795" spans="8:11" x14ac:dyDescent="0.3">
@@ -6823,6 +6850,7 @@
     <row r="807" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H807" s="2"/>
       <c r="I807" s="1"/>
+      <c r="J807" s="2"/>
       <c r="K807" s="1"/>
     </row>
     <row r="808" spans="8:11" x14ac:dyDescent="0.3">
@@ -40331,7 +40359,845 @@
       <c r="J6919" s="2"/>
       <c r="K6919" s="1"/>
     </row>
+    <row r="6920" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6920" s="2"/>
+      <c r="K6920" s="1"/>
+    </row>
+    <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6921" s="1"/>
+    </row>
+    <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6922" s="2"/>
+      <c r="K6922" s="1"/>
+    </row>
+    <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6923" s="1"/>
+    </row>
+    <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6924" s="2"/>
+      <c r="K6924" s="1"/>
+    </row>
+    <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6925" s="1"/>
+    </row>
+    <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6926" s="2"/>
+      <c r="K6926" s="1"/>
+    </row>
+    <row r="6927" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6927" s="2"/>
+      <c r="K6927" s="1"/>
+    </row>
+    <row r="6928" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6928" s="2"/>
+      <c r="K6928" s="1"/>
+    </row>
+    <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6929" s="1"/>
+    </row>
+    <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6930" s="1"/>
+    </row>
+    <row r="6931" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6931" s="1"/>
+    </row>
+    <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6932" s="1"/>
+    </row>
+    <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6933" s="2"/>
+      <c r="K6933" s="1"/>
+    </row>
+    <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6934" s="1"/>
+    </row>
+    <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6936" s="1"/>
+    </row>
+    <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6937" s="2"/>
+      <c r="K6937" s="1"/>
+    </row>
+    <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6938" s="1"/>
+    </row>
+    <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6939" s="1"/>
+    </row>
+    <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6940" s="1"/>
+    </row>
+    <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6941" s="2"/>
+      <c r="K6941" s="1"/>
+    </row>
+    <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6942" s="1"/>
+    </row>
+    <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6943" s="1"/>
+    </row>
+    <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6944" s="1"/>
+    </row>
+    <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6945" s="2"/>
+      <c r="K6945" s="1"/>
+    </row>
+    <row r="6946" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6946" s="2"/>
+      <c r="K6946" s="1"/>
+    </row>
+    <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6947" s="1"/>
+    </row>
+    <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6948" s="1"/>
+    </row>
+    <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6949" s="2"/>
+      <c r="K6949" s="1"/>
+    </row>
+    <row r="6950" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6950" s="1"/>
+    </row>
+    <row r="6951" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6951" s="2"/>
+      <c r="K6951" s="1"/>
+    </row>
+    <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6952" s="1"/>
+    </row>
+    <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6953" s="2"/>
+      <c r="K6953" s="1"/>
+    </row>
+    <row r="6954" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6954" s="2"/>
+      <c r="K6954" s="1"/>
+    </row>
+    <row r="6955" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6955" s="2"/>
+      <c r="K6955" s="1"/>
+    </row>
+    <row r="6956" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6956" s="1"/>
+    </row>
+    <row r="6957" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6957" s="2"/>
+      <c r="K6957" s="1"/>
+    </row>
+    <row r="6958" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6958" s="2"/>
+      <c r="K6958" s="1"/>
+    </row>
+    <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6959" s="1"/>
+    </row>
+    <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6960" s="2"/>
+      <c r="K6960" s="1"/>
+    </row>
+    <row r="6961" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6961" s="2"/>
+      <c r="K6961" s="1"/>
+    </row>
+    <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6963" s="1"/>
+    </row>
+    <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6964" s="2"/>
+      <c r="K6964" s="1"/>
+    </row>
+    <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6965" s="1"/>
+    </row>
+    <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6966" s="2"/>
+      <c r="K6966" s="1"/>
+    </row>
+    <row r="6967" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6967" s="2"/>
+      <c r="K6967" s="1"/>
+    </row>
+    <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6968" s="1"/>
+    </row>
+    <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6969" s="2"/>
+      <c r="K6969" s="1"/>
+    </row>
+    <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6970" s="1"/>
+    </row>
+    <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6971" s="2"/>
+      <c r="K6971" s="1"/>
+    </row>
+    <row r="6972" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6972" s="2"/>
+      <c r="K6972" s="1"/>
+    </row>
+    <row r="6973" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6973" s="1"/>
+    </row>
+    <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6974" s="1"/>
+    </row>
+    <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6975" s="2"/>
+      <c r="K6975" s="1"/>
+    </row>
+    <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6977" s="1"/>
+    </row>
+    <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6978" s="2"/>
+      <c r="K6978" s="1"/>
+    </row>
+    <row r="6979" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6979" s="1"/>
+    </row>
+    <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6980" s="1"/>
+    </row>
+    <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6981" s="1"/>
+    </row>
+    <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6982" s="1"/>
+    </row>
+    <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6983" s="1"/>
+    </row>
+    <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6984" s="2"/>
+      <c r="K6984" s="1"/>
+    </row>
+    <row r="6985" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6985" s="2"/>
+      <c r="K6985" s="1"/>
+    </row>
+    <row r="6986" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6986" s="2"/>
+      <c r="K6986" s="1"/>
+    </row>
+    <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6987" s="1"/>
+    </row>
+    <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6988" s="2"/>
+      <c r="K6988" s="1"/>
+    </row>
+    <row r="6989" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6989" s="2"/>
+      <c r="K6989" s="1"/>
+    </row>
+    <row r="6990" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6990" s="2"/>
+      <c r="K6990" s="1"/>
+    </row>
+    <row r="6991" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6991" s="1"/>
+    </row>
+    <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6992" s="1"/>
+    </row>
+    <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6993" s="2"/>
+      <c r="K6993" s="1"/>
+    </row>
+    <row r="6994" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6994" s="2"/>
+      <c r="K6994" s="1"/>
+    </row>
+    <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6995" s="1"/>
+    </row>
+    <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6996" s="2"/>
+      <c r="K6996" s="1"/>
+    </row>
+    <row r="6997" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6997" s="1"/>
+    </row>
+    <row r="6998" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6998" s="1"/>
+    </row>
+    <row r="6999" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6999" s="2"/>
+      <c r="K6999" s="1"/>
+    </row>
+    <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7000" s="1"/>
+    </row>
+    <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7001" s="1"/>
+    </row>
+    <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7002" s="1"/>
+    </row>
+    <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7003" s="1"/>
+    </row>
+    <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7004" s="1"/>
+    </row>
+    <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7005" s="2"/>
+      <c r="K7005" s="1"/>
+    </row>
+    <row r="7006" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7006" s="1"/>
+    </row>
+    <row r="7007" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7007" s="2"/>
+      <c r="K7007" s="1"/>
+    </row>
+    <row r="7008" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7008" s="2"/>
+      <c r="K7008" s="1"/>
+    </row>
+    <row r="7009" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7009" s="1"/>
+    </row>
+    <row r="7011" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7011" s="2"/>
+      <c r="K7011" s="1"/>
+    </row>
+    <row r="7012" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7012" s="1"/>
+    </row>
+    <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7014" s="1"/>
+    </row>
+    <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7015" s="2"/>
+      <c r="K7015" s="1"/>
+    </row>
+    <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7016" s="1"/>
+    </row>
+    <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7017" s="1"/>
+    </row>
+    <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7018" s="2"/>
+      <c r="K7018" s="1"/>
+    </row>
+    <row r="7019" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7019" s="2"/>
+      <c r="K7019" s="1"/>
+    </row>
+    <row r="7020" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7020" s="2"/>
+      <c r="K7020" s="1"/>
+    </row>
+    <row r="7021" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7021" s="1"/>
+    </row>
+    <row r="7022" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7022" s="2"/>
+      <c r="K7022" s="1"/>
+    </row>
+    <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7023" s="1"/>
+    </row>
+    <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7024" s="1"/>
+    </row>
+    <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7025" s="1"/>
+    </row>
+    <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7026" s="2"/>
+      <c r="K7026" s="1"/>
+    </row>
+    <row r="7027" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7027" s="2"/>
+      <c r="K7027" s="1"/>
+    </row>
+    <row r="7028" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7028" s="1"/>
+    </row>
+    <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7030" s="1"/>
+    </row>
+    <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7031" s="1"/>
+    </row>
+    <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7032" s="2"/>
+      <c r="K7032" s="1"/>
+    </row>
+    <row r="7033" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7033" s="2"/>
+      <c r="K7033" s="1"/>
+    </row>
+    <row r="7034" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7034" s="2"/>
+      <c r="K7034" s="1"/>
+    </row>
+    <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7035" s="1"/>
+    </row>
+    <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7036" s="1"/>
+    </row>
+    <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7037" s="1"/>
+    </row>
+    <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7038" s="1"/>
+    </row>
+    <row r="7039" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7039" s="1"/>
+    </row>
+    <row r="7040" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7040" s="1"/>
+    </row>
+    <row r="7041" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7041" s="2"/>
+      <c r="K7041" s="1"/>
+    </row>
+    <row r="7042" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7042" s="2"/>
+      <c r="K7042" s="1"/>
+    </row>
+    <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7043" s="1"/>
+    </row>
+    <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7044" s="2"/>
+      <c r="K7044" s="1"/>
+    </row>
+    <row r="7045" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7045" s="2"/>
+      <c r="K7045" s="1"/>
+    </row>
+    <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7046" s="1"/>
+    </row>
+    <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7047" s="1"/>
+    </row>
+    <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7048" s="2"/>
+      <c r="K7048" s="1"/>
+    </row>
+    <row r="7049" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7049" s="2"/>
+      <c r="K7049" s="1"/>
+    </row>
+    <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7050" s="1"/>
+    </row>
+    <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7051" s="2"/>
+      <c r="K7051" s="1"/>
+    </row>
+    <row r="7052" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7052" s="2"/>
+      <c r="K7052" s="1"/>
+    </row>
+    <row r="7053" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7053" s="2"/>
+      <c r="K7053" s="1"/>
+    </row>
+    <row r="7054" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7054" s="2"/>
+      <c r="K7054" s="1"/>
+    </row>
+    <row r="7055" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7055" s="2"/>
+      <c r="K7055" s="1"/>
+    </row>
+    <row r="7056" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7056" s="2"/>
+      <c r="K7056" s="1"/>
+    </row>
+    <row r="7057" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7057" s="2"/>
+      <c r="K7057" s="1"/>
+    </row>
+    <row r="7058" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7058" s="2"/>
+      <c r="K7058" s="1"/>
+    </row>
+    <row r="7059" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7059" s="2"/>
+      <c r="K7059" s="1"/>
+    </row>
+    <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7060" s="1"/>
+    </row>
+    <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7061" s="1"/>
+    </row>
+    <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7062" s="2"/>
+      <c r="K7062" s="1"/>
+    </row>
+    <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7063" s="1"/>
+    </row>
+    <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7064" s="1"/>
+    </row>
+    <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7065" s="1"/>
+    </row>
+    <row r="7066" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7066" s="2"/>
+      <c r="K7066" s="1"/>
+    </row>
+    <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7067" s="1"/>
+    </row>
+    <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7068" s="2"/>
+      <c r="K7068" s="1"/>
+    </row>
+    <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7069" s="1"/>
+    </row>
+    <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7071" s="1"/>
+    </row>
+    <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7072" s="1"/>
+    </row>
+    <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7073" s="1"/>
+    </row>
+    <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7074" s="1"/>
+    </row>
+    <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7075" s="2"/>
+      <c r="K7075" s="1"/>
+    </row>
+    <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7076" s="1"/>
+    </row>
+    <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7077" s="2"/>
+      <c r="K7077" s="1"/>
+    </row>
+    <row r="7078" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7078" s="1"/>
+    </row>
+    <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7079" s="1"/>
+    </row>
+    <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7080" s="2"/>
+      <c r="K7080" s="1"/>
+    </row>
+    <row r="7081" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7081" s="2"/>
+      <c r="K7081" s="1"/>
+    </row>
+    <row r="7082" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7082" s="1"/>
+    </row>
+    <row r="7083" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7083" s="2"/>
+      <c r="K7083" s="1"/>
+    </row>
+    <row r="7084" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7084" s="2"/>
+      <c r="K7084" s="1"/>
+    </row>
+    <row r="7085" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7085" s="2"/>
+      <c r="K7085" s="1"/>
+    </row>
+    <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7086" s="1"/>
+    </row>
+    <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7087" s="1"/>
+    </row>
+    <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7088" s="1"/>
+    </row>
+    <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7089" s="1"/>
+    </row>
+    <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7090" s="1"/>
+    </row>
+    <row r="7091" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7091" s="1"/>
+    </row>
+    <row r="7092" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7092" s="2"/>
+      <c r="K7092" s="1"/>
+    </row>
+    <row r="7093" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7093" s="2"/>
+      <c r="K7093" s="1"/>
+    </row>
+    <row r="7094" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7094" s="2"/>
+      <c r="K7094" s="1"/>
+    </row>
+    <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7095" s="1"/>
+    </row>
+    <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7096" s="2"/>
+      <c r="K7096" s="1"/>
+    </row>
+    <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7097" s="1"/>
+    </row>
+    <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7098" s="1"/>
+    </row>
+    <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7099" s="2"/>
+      <c r="K7099" s="1"/>
+    </row>
+    <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7100" s="1"/>
+    </row>
+    <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7101" s="2"/>
+      <c r="K7101" s="1"/>
+    </row>
+    <row r="7102" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7102" s="2"/>
+      <c r="K7102" s="1"/>
+    </row>
+    <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7103" s="1"/>
+    </row>
+    <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7104" s="2"/>
+      <c r="K7104" s="1"/>
+    </row>
+    <row r="7105" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7105" s="2"/>
+      <c r="K7105" s="1"/>
+    </row>
+    <row r="7106" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7106" s="2"/>
+      <c r="K7106" s="1"/>
+    </row>
+    <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7108" s="2"/>
+      <c r="K7108" s="1"/>
+    </row>
+    <row r="7109" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7109" s="2"/>
+      <c r="K7109" s="1"/>
+    </row>
+    <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7110" s="1"/>
+    </row>
+    <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7111" s="2"/>
+      <c r="K7111" s="1"/>
+    </row>
+    <row r="7112" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7112" s="2"/>
+      <c r="K7112" s="1"/>
+    </row>
+    <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7113" s="1"/>
+    </row>
+    <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7114" s="2"/>
+      <c r="K7114" s="1"/>
+    </row>
+    <row r="7115" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7115" s="2"/>
+      <c r="K7115" s="1"/>
+    </row>
+    <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7117" s="1"/>
+    </row>
+    <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7118" s="1"/>
+    </row>
+    <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7119" s="2"/>
+      <c r="K7119" s="1"/>
+    </row>
+    <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7120" s="1"/>
+    </row>
+    <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7121" s="2"/>
+      <c r="K7121" s="1"/>
+    </row>
+    <row r="7122" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7122" s="2"/>
+      <c r="K7122" s="1"/>
+    </row>
+    <row r="7123" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7123" s="1"/>
+    </row>
+    <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7124" s="1"/>
+    </row>
+    <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7125" s="2"/>
+      <c r="K7125" s="1"/>
+    </row>
+    <row r="7126" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7126" s="2"/>
+      <c r="K7126" s="1"/>
+    </row>
+    <row r="7127" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7127" s="1"/>
+    </row>
+    <row r="7128" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7128" s="2"/>
+      <c r="K7128" s="1"/>
+    </row>
+    <row r="7129" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7129" s="2"/>
+      <c r="K7129" s="1"/>
+    </row>
+    <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7130" s="1"/>
+    </row>
+    <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7131" s="2"/>
+      <c r="K7131" s="1"/>
+    </row>
+    <row r="7132" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7132" s="2"/>
+      <c r="K7132" s="1"/>
+    </row>
+    <row r="7133" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7133" s="2"/>
+      <c r="K7133" s="1"/>
+    </row>
+    <row r="7134" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7134" s="2"/>
+      <c r="K7134" s="1"/>
+    </row>
+    <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7135" s="1"/>
+    </row>
+    <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7136" s="1"/>
+    </row>
+    <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7137" s="1"/>
+    </row>
+    <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7138" s="2"/>
+      <c r="K7138" s="1"/>
+    </row>
+    <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7140" s="1"/>
+    </row>
+    <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7141" s="2"/>
+      <c r="K7141" s="1"/>
+    </row>
+    <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7143" s="1"/>
+    </row>
+    <row r="7144" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7144" s="1"/>
+    </row>
+    <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7145" s="1"/>
+    </row>
+    <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7146" s="2"/>
+      <c r="K7146" s="1"/>
+    </row>
+    <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7147" s="1"/>
+    </row>
+    <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7148" s="1"/>
+    </row>
+    <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7150" s="1"/>
+    </row>
+    <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7151" s="1"/>
+    </row>
+    <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7152" s="2"/>
+      <c r="K7152" s="1"/>
+    </row>
+    <row r="7153" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7153" s="1"/>
+    </row>
+    <row r="7154" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7154" s="1"/>
+    </row>
+    <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7155" s="1"/>
+    </row>
+    <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7156" s="2"/>
+      <c r="K7156" s="1"/>
+    </row>
+    <row r="7157" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7157" s="1"/>
+    </row>
+    <row r="7158" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7158" s="2"/>
+      <c r="K7158" s="1"/>
+    </row>
+    <row r="7159" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7159" s="2"/>
+      <c r="K7159" s="1"/>
+    </row>
+    <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7160" s="1"/>
+    </row>
+    <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7161" s="1"/>
+    </row>
+    <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7162" s="2"/>
+      <c r="K7162" s="1"/>
+    </row>
+    <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7163" s="1"/>
+    </row>
+    <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7164" s="1"/>
+    </row>
+    <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7165" s="2"/>
+      <c r="K7165" s="1"/>
+    </row>
+    <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7166" s="1"/>
+    </row>
+    <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7167" s="1"/>
+    </row>
+    <row r="7168" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7168" s="1"/>
+    </row>
+    <row r="7169" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7169" s="1"/>
+    </row>
+    <row r="7170" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7170" s="2"/>
+      <c r="K7170" s="1"/>
+    </row>
+    <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7171" s="1"/>
+    </row>
+    <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7172" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Indigo-Construction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{36A2F0FA-12AF-4B7C-8AEE-06D28F59C827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9FA665C9-E761-4B8A-BAD7-BE2924E42F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="40">
   <si>
     <t>Company Name</t>
   </si>
@@ -86,31 +86,34 @@
     <t>UNKNOWN</t>
   </si>
   <si>
-    <t>Speed Management</t>
+    <t>Mark Complete</t>
+  </si>
+  <si>
+    <t>Camera Event Management Orientation for Drivers</t>
+  </si>
+  <si>
+    <t>Big Wins Through Behavior Change</t>
   </si>
   <si>
     <t>Rules for Safe Driving</t>
   </si>
   <si>
-    <t>Drowsy Driving</t>
+    <t>Driver Health</t>
   </si>
   <si>
-    <t>Mark Complete</t>
+    <t>Speed Management</t>
   </si>
   <si>
     <t>Alert Driving: Big Three</t>
+  </si>
+  <si>
+    <t>Drowsy Driving</t>
   </si>
   <si>
     <t>Space Management for Commercial Vehicles</t>
   </si>
   <si>
     <t>Speed Mangement-C</t>
-  </si>
-  <si>
-    <t>Camera Event Management Orientation for Drivers</t>
-  </si>
-  <si>
-    <t>Big Wins Through Behavior Change</t>
   </si>
   <si>
     <t>Indigo Construction</t>
@@ -147,6 +150,15 @@
   </si>
   <si>
     <t>Jesse Garcia</t>
+  </si>
+  <si>
+    <t>Jason Edwards</t>
+  </si>
+  <si>
+    <t>Sergio Costilla de leon</t>
+  </si>
+  <si>
+    <t>Stephen Hails</t>
   </si>
 </sst>
 </file>
@@ -520,7 +532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M7172"/>
+  <dimension ref="D1:M7173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -569,16 +581,16 @@
     </row>
     <row r="2" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2">
         <v>5162</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>12</v>
@@ -602,21 +614,21 @@
       <c r="J3" s="2"/>
       <c r="K3" s="1"/>
       <c r="M3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4">
         <v>5166</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>13</v>
@@ -636,16 +648,16 @@
     </row>
     <row r="5" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5">
         <v>5168</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>10</v>
@@ -665,16 +677,16 @@
     </row>
     <row r="6" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6">
         <v>5163</v>
       </c>
       <c r="F6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>13</v>
@@ -694,16 +706,16 @@
     </row>
     <row r="7" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E7">
         <v>5159</v>
       </c>
       <c r="F7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>13</v>
@@ -723,16 +735,16 @@
     </row>
     <row r="8" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E8">
         <v>5165</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>13</v>
@@ -752,16 +764,16 @@
     </row>
     <row r="9" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E9">
         <v>5160</v>
       </c>
       <c r="F9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>13</v>
@@ -781,16 +793,16 @@
     </row>
     <row r="10" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E10">
         <v>5161</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>10</v>
@@ -810,16 +822,16 @@
     </row>
     <row r="11" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E11">
         <v>5167</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>13</v>
@@ -839,16 +851,16 @@
     </row>
     <row r="12" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E12">
         <v>5164</v>
       </c>
       <c r="F12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>13</v>
@@ -868,16 +880,16 @@
     </row>
     <row r="13" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E13">
         <v>5162</v>
       </c>
       <c r="F13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>13</v>
@@ -897,16 +909,16 @@
     </row>
     <row r="14" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E14">
         <v>5166</v>
       </c>
       <c r="F14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>12</v>
@@ -930,21 +942,21 @@
       <c r="J15" s="2"/>
       <c r="K15" s="1"/>
       <c r="M15" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E16">
         <v>5168</v>
       </c>
       <c r="F16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>13</v>
@@ -964,16 +976,16 @@
     </row>
     <row r="17" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E17">
         <v>5163</v>
       </c>
       <c r="F17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>13</v>
@@ -993,16 +1005,16 @@
     </row>
     <row r="18" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E18">
         <v>5159</v>
       </c>
       <c r="F18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>13</v>
@@ -1022,16 +1034,16 @@
     </row>
     <row r="19" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E19">
         <v>5165</v>
       </c>
       <c r="F19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>13</v>
@@ -1051,16 +1063,16 @@
     </row>
     <row r="20" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E20">
         <v>5160</v>
       </c>
       <c r="F20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>12</v>
@@ -1084,21 +1096,21 @@
       <c r="J21" s="2"/>
       <c r="K21" s="1"/>
       <c r="M21" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E22">
         <v>5161</v>
       </c>
       <c r="F22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>13</v>
@@ -1118,16 +1130,16 @@
     </row>
     <row r="23" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E23">
         <v>5167</v>
       </c>
       <c r="F23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>13</v>
@@ -1147,16 +1159,16 @@
     </row>
     <row r="24" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E24">
         <v>5164</v>
       </c>
       <c r="F24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>12</v>
@@ -1180,21 +1192,21 @@
       <c r="J25" s="2"/>
       <c r="K25" s="1"/>
       <c r="M25" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D26" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E26">
         <v>5162</v>
       </c>
       <c r="F26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>13</v>
@@ -1214,16 +1226,16 @@
     </row>
     <row r="27" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E27">
         <v>5166</v>
       </c>
       <c r="F27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>13</v>
@@ -1243,16 +1255,16 @@
     </row>
     <row r="28" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D28" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E28">
         <v>5168</v>
       </c>
       <c r="F28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>13</v>
@@ -1272,16 +1284,16 @@
     </row>
     <row r="29" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D29" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E29">
         <v>5163</v>
       </c>
       <c r="F29" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>13</v>
@@ -1301,16 +1313,16 @@
     </row>
     <row r="30" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E30">
         <v>5159</v>
       </c>
       <c r="F30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>13</v>
@@ -1330,16 +1342,16 @@
     </row>
     <row r="31" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D31" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E31">
         <v>5165</v>
       </c>
       <c r="F31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>13</v>
@@ -1359,16 +1371,16 @@
     </row>
     <row r="32" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D32" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E32">
         <v>5160</v>
       </c>
       <c r="F32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>12</v>
@@ -1392,21 +1404,21 @@
       <c r="J33" s="2"/>
       <c r="K33" s="1"/>
       <c r="M33" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D34" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E34">
         <v>5161</v>
       </c>
       <c r="F34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>13</v>
@@ -1426,16 +1438,16 @@
     </row>
     <row r="35" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D35" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E35">
         <v>5167</v>
       </c>
       <c r="F35" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>13</v>
@@ -1455,16 +1467,16 @@
     </row>
     <row r="36" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D36" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E36">
         <v>5164</v>
       </c>
       <c r="F36" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>13</v>
@@ -1484,16 +1496,16 @@
     </row>
     <row r="37" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D37" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E37">
         <v>5162</v>
       </c>
       <c r="F37" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>13</v>
@@ -1513,16 +1525,16 @@
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D38" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E38">
         <v>5166</v>
       </c>
       <c r="F38" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>13</v>
@@ -1542,16 +1554,16 @@
     </row>
     <row r="39" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D39" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E39">
         <v>5168</v>
       </c>
       <c r="F39" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>13</v>
@@ -1571,16 +1583,16 @@
     </row>
     <row r="40" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D40" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E40">
         <v>5163</v>
       </c>
       <c r="F40" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>13</v>
@@ -1600,16 +1612,16 @@
     </row>
     <row r="41" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D41" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E41">
         <v>5159</v>
       </c>
       <c r="F41" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>13</v>
@@ -1629,16 +1641,16 @@
     </row>
     <row r="42" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D42" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E42">
         <v>5165</v>
       </c>
       <c r="F42" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>13</v>
@@ -1658,16 +1670,16 @@
     </row>
     <row r="43" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D43" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E43">
         <v>5160</v>
       </c>
       <c r="F43" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>13</v>
@@ -1687,16 +1699,16 @@
     </row>
     <row r="44" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D44" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E44">
         <v>5161</v>
       </c>
       <c r="F44" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>13</v>
@@ -1716,16 +1728,16 @@
     </row>
     <row r="45" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D45" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E45">
         <v>5167</v>
       </c>
       <c r="F45" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>13</v>
@@ -1745,16 +1757,16 @@
     </row>
     <row r="46" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D46" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E46">
         <v>5164</v>
       </c>
       <c r="F46" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>14</v>
@@ -1778,21 +1790,21 @@
       <c r="J47" s="2"/>
       <c r="K47" s="1"/>
       <c r="M47" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D48" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E48">
         <v>5162</v>
       </c>
       <c r="F48" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>10</v>
@@ -1812,16 +1824,16 @@
     </row>
     <row r="49" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D49" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E49">
         <v>5166</v>
       </c>
       <c r="F49" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>14</v>
@@ -1845,21 +1857,21 @@
       <c r="J50" s="2"/>
       <c r="K50" s="1"/>
       <c r="M50" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D51" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E51">
         <v>5168</v>
       </c>
       <c r="F51" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>10</v>
@@ -1879,16 +1891,16 @@
     </row>
     <row r="52" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D52" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E52">
         <v>5163</v>
       </c>
       <c r="F52" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>13</v>
@@ -1908,16 +1920,16 @@
     </row>
     <row r="53" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D53" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E53">
         <v>5159</v>
       </c>
       <c r="F53" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>10</v>
@@ -1937,16 +1949,16 @@
     </row>
     <row r="54" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D54" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E54">
         <v>5165</v>
       </c>
       <c r="F54" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>10</v>
@@ -1966,16 +1978,16 @@
     </row>
     <row r="55" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D55" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E55">
         <v>5160</v>
       </c>
       <c r="F55" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>10</v>
@@ -1995,16 +2007,16 @@
     </row>
     <row r="56" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D56" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E56">
         <v>5161</v>
       </c>
       <c r="F56" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>13</v>
@@ -2024,16 +2036,16 @@
     </row>
     <row r="57" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D57" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E57">
         <v>5167</v>
       </c>
       <c r="F57" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>12</v>
@@ -2057,21 +2069,21 @@
       <c r="J58" s="2"/>
       <c r="K58" s="1"/>
       <c r="M58" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D59" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E59">
         <v>5164</v>
       </c>
       <c r="F59" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>10</v>
@@ -2091,16 +2103,16 @@
     </row>
     <row r="60" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E60">
         <v>5668</v>
       </c>
       <c r="F60" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>10</v>
@@ -2120,16 +2132,16 @@
     </row>
     <row r="61" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D61" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E61">
         <v>5167</v>
       </c>
       <c r="F61" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>10</v>
@@ -2149,16 +2161,16 @@
     </row>
     <row r="62" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D62" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E62">
         <v>5168</v>
       </c>
       <c r="F62" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>10</v>
@@ -2178,16 +2190,16 @@
     </row>
     <row r="63" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D63" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E63">
         <v>5162</v>
       </c>
       <c r="F63" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>10</v>
@@ -2207,16 +2219,16 @@
     </row>
     <row r="64" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D64" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E64">
         <v>5166</v>
       </c>
       <c r="F64" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>12</v>
@@ -2240,21 +2252,21 @@
       <c r="J65" s="2"/>
       <c r="K65" s="1"/>
       <c r="M65" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D66" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E66">
         <v>5163</v>
       </c>
       <c r="F66" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>13</v>
@@ -2274,16 +2286,16 @@
     </row>
     <row r="67" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D67" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E67">
         <v>5159</v>
       </c>
       <c r="F67" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>10</v>
@@ -2303,16 +2315,16 @@
     </row>
     <row r="68" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D68" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E68">
         <v>5165</v>
       </c>
       <c r="F68" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>10</v>
@@ -2332,16 +2344,16 @@
     </row>
     <row r="69" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D69" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E69">
         <v>5160</v>
       </c>
       <c r="F69" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>10</v>
@@ -2361,16 +2373,16 @@
     </row>
     <row r="70" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D70" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E70">
         <v>5161</v>
       </c>
       <c r="F70" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>13</v>
@@ -2390,16 +2402,16 @@
     </row>
     <row r="71" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D71" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E71">
         <v>5164</v>
       </c>
       <c r="F71" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>12</v>
@@ -2423,27 +2435,27 @@
       <c r="J72" s="2"/>
       <c r="K72" s="1"/>
       <c r="M72" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="73" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D73" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E73">
         <v>5668</v>
       </c>
       <c r="F73" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J73" s="2">
-        <v>9.0277777777777769E-3</v>
+        <v>8.4259259259259256E-2</v>
       </c>
       <c r="K73" s="1">
         <v>46209.043287037035</v>
@@ -2456,141 +2468,458 @@
       </c>
     </row>
     <row r="74" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H74" s="2"/>
-      <c r="I74" s="1"/>
-      <c r="J74" s="2"/>
-      <c r="K74" s="1"/>
+      <c r="D74" t="s">
+        <v>25</v>
+      </c>
+      <c r="E74">
+        <v>5162</v>
+      </c>
+      <c r="F74" t="s">
+        <v>26</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J74" s="2">
+        <v>6.5046296296296293E-3</v>
+      </c>
+      <c r="K74" s="1">
+        <v>46219.693749999999</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
       <c r="M74" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="75" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H75" s="2"/>
-      <c r="I75" s="1"/>
-      <c r="J75" s="2"/>
-      <c r="K75" s="1"/>
+      <c r="D75" t="s">
+        <v>25</v>
+      </c>
+      <c r="E75">
+        <v>5166</v>
+      </c>
+      <c r="F75" t="s">
+        <v>27</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J75" s="2">
+        <v>0</v>
+      </c>
+      <c r="K75" s="1">
+        <v>46219.668865740743</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="76" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H76" s="2"/>
-      <c r="I76" s="1"/>
-      <c r="J76" s="2"/>
-      <c r="K76" s="1"/>
+      <c r="D76" t="s">
+        <v>25</v>
+      </c>
+      <c r="E76">
+        <v>5168</v>
+      </c>
+      <c r="F76" t="s">
+        <v>28</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J76" s="2">
+        <v>0</v>
+      </c>
+      <c r="K76" s="1">
+        <v>46219.669560185182</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="77" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H77" s="2"/>
       <c r="I77" s="1"/>
       <c r="J77" s="2"/>
       <c r="K77" s="1"/>
+      <c r="M77" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="78" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H78" s="2"/>
-      <c r="I78" s="1"/>
-      <c r="J78" s="2"/>
-      <c r="K78" s="1"/>
+      <c r="D78" t="s">
+        <v>25</v>
+      </c>
+      <c r="E78">
+        <v>5938</v>
+      </c>
+      <c r="F78" t="s">
+        <v>37</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J78" s="2">
+        <v>2.3148148148148147E-5</v>
+      </c>
+      <c r="K78" s="1">
+        <v>46219.669560185182</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="79" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H79" s="2"/>
       <c r="I79" s="1"/>
       <c r="J79" s="2"/>
       <c r="K79" s="1"/>
+      <c r="M79" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="80" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H80" s="2"/>
-      <c r="I80" s="1"/>
-      <c r="J80" s="2"/>
-      <c r="K80" s="1"/>
-    </row>
-    <row r="81" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H81" s="2"/>
-      <c r="I81" s="1"/>
-      <c r="J81" s="2"/>
-      <c r="K81" s="1"/>
-    </row>
-    <row r="82" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H82" s="2"/>
-      <c r="I82" s="1"/>
-      <c r="J82" s="2"/>
-      <c r="K82" s="1"/>
-    </row>
-    <row r="83" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="D80" t="s">
+        <v>25</v>
+      </c>
+      <c r="E80">
+        <v>5668</v>
+      </c>
+      <c r="F80" t="s">
+        <v>36</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J80" s="2">
+        <v>1.0578703703703703E-2</v>
+      </c>
+      <c r="K80" s="1">
+        <v>46219.670254629629</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="81" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D81" t="s">
+        <v>25</v>
+      </c>
+      <c r="E81">
+        <v>5163</v>
+      </c>
+      <c r="F81" t="s">
+        <v>29</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J81" s="2">
+        <v>0</v>
+      </c>
+      <c r="K81" s="1">
+        <v>46219.670949074076</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="82" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D82" t="s">
+        <v>25</v>
+      </c>
+      <c r="E82">
+        <v>5159</v>
+      </c>
+      <c r="F82" t="s">
+        <v>30</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J82" s="2">
+        <v>0</v>
+      </c>
+      <c r="K82" s="1">
+        <v>46219.671643518515</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="83" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H83" s="2"/>
       <c r="I83" s="1"/>
       <c r="J83" s="2"/>
       <c r="K83" s="1"/>
-    </row>
-    <row r="84" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H84" s="2"/>
-      <c r="I84" s="1"/>
-      <c r="J84" s="2"/>
-      <c r="K84" s="1"/>
-    </row>
-    <row r="85" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="M83" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D84" t="s">
+        <v>25</v>
+      </c>
+      <c r="E84">
+        <v>5165</v>
+      </c>
+      <c r="F84" t="s">
+        <v>31</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J84" s="2">
+        <v>0</v>
+      </c>
+      <c r="K84" s="1">
+        <v>46219.671643518515</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="85" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H85" s="2"/>
       <c r="I85" s="1"/>
       <c r="J85" s="2"/>
       <c r="K85" s="1"/>
-    </row>
-    <row r="86" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H86" s="2"/>
-      <c r="I86" s="1"/>
-      <c r="J86" s="2"/>
-      <c r="K86" s="1"/>
-    </row>
-    <row r="87" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H87" s="2"/>
-      <c r="I87" s="1"/>
-      <c r="J87" s="2"/>
-      <c r="K87" s="1"/>
-    </row>
-    <row r="88" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="M85" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="86" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D86" t="s">
+        <v>25</v>
+      </c>
+      <c r="E86">
+        <v>5160</v>
+      </c>
+      <c r="F86" t="s">
+        <v>32</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J86" s="2">
+        <v>7.6041666666666671E-3</v>
+      </c>
+      <c r="K86" s="1">
+        <v>46219.672337962962</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="87" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D87" t="s">
+        <v>25</v>
+      </c>
+      <c r="E87">
+        <v>5167</v>
+      </c>
+      <c r="F87" t="s">
+        <v>34</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J87" s="2">
+        <v>0</v>
+      </c>
+      <c r="K87" s="1">
+        <v>46219.673032407409</v>
+      </c>
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="88" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H88" s="2"/>
       <c r="I88" s="1"/>
       <c r="J88" s="2"/>
       <c r="K88" s="1"/>
-    </row>
-    <row r="89" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H89" s="2"/>
-      <c r="I89" s="1"/>
-      <c r="J89" s="2"/>
-      <c r="K89" s="1"/>
-    </row>
-    <row r="90" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H90" s="2"/>
-      <c r="I90" s="1"/>
-      <c r="J90" s="2"/>
-      <c r="K90" s="1"/>
-    </row>
-    <row r="91" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="M88" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="89" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D89" t="s">
+        <v>25</v>
+      </c>
+      <c r="E89">
+        <v>5164</v>
+      </c>
+      <c r="F89" t="s">
+        <v>35</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J89" s="2">
+        <v>8.1712962962962963E-3</v>
+      </c>
+      <c r="K89" s="1">
+        <v>46219.673032407409</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D90" t="s">
+        <v>25</v>
+      </c>
+      <c r="E90">
+        <v>5937</v>
+      </c>
+      <c r="F90" t="s">
+        <v>38</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J90" s="2">
+        <v>0</v>
+      </c>
+      <c r="K90" s="1">
+        <v>46219.673726851855</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H91" s="2"/>
       <c r="I91" s="1"/>
       <c r="J91" s="2"/>
       <c r="K91" s="1"/>
-    </row>
-    <row r="92" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H92" s="2"/>
-      <c r="I92" s="1"/>
-      <c r="J92" s="2"/>
-      <c r="K92" s="1"/>
-    </row>
-    <row r="93" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="M91" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="92" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D92" t="s">
+        <v>25</v>
+      </c>
+      <c r="E92">
+        <v>5936</v>
+      </c>
+      <c r="F92" t="s">
+        <v>39</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J92" s="2">
+        <v>0</v>
+      </c>
+      <c r="K92" s="1">
+        <v>46219.674421296295</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="93" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H93" s="2"/>
       <c r="I93" s="1"/>
       <c r="J93" s="2"/>
       <c r="K93" s="1"/>
-    </row>
-    <row r="94" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="M93" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H94" s="2"/>
       <c r="I94" s="1"/>
       <c r="J94" s="2"/>
       <c r="K94" s="1"/>
     </row>
-    <row r="95" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="95" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H95" s="2"/>
       <c r="I95" s="1"/>
       <c r="J95" s="2"/>
       <c r="K95" s="1"/>
     </row>
-    <row r="96" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="96" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H96" s="2"/>
       <c r="I96" s="1"/>
       <c r="J96" s="2"/>
@@ -6705,6 +7034,7 @@
     </row>
     <row r="782" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I782" s="1"/>
+      <c r="J782" s="2"/>
       <c r="K782" s="1"/>
     </row>
     <row r="783" spans="8:11" x14ac:dyDescent="0.3">
@@ -6734,6 +7064,7 @@
     <row r="787" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H787" s="2"/>
       <c r="I787" s="1"/>
+      <c r="J787" s="2"/>
       <c r="K787" s="1"/>
     </row>
     <row r="788" spans="8:11" x14ac:dyDescent="0.3">
@@ -6799,6 +7130,7 @@
     <row r="798" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H798" s="2"/>
       <c r="I798" s="1"/>
+      <c r="J798" s="2"/>
       <c r="K798" s="1"/>
     </row>
     <row r="799" spans="8:11" x14ac:dyDescent="0.3">
@@ -6822,6 +7154,7 @@
     <row r="802" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H802" s="2"/>
       <c r="I802" s="1"/>
+      <c r="J802" s="2"/>
       <c r="K802" s="1"/>
     </row>
     <row r="803" spans="8:11" x14ac:dyDescent="0.3">
@@ -6839,6 +7172,7 @@
     <row r="805" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H805" s="2"/>
       <c r="I805" s="1"/>
+      <c r="J805" s="2"/>
       <c r="K805" s="1"/>
     </row>
     <row r="806" spans="8:11" x14ac:dyDescent="0.3">
@@ -6856,6 +7190,7 @@
     <row r="808" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H808" s="2"/>
       <c r="I808" s="1"/>
+      <c r="J808" s="2"/>
       <c r="K808" s="1"/>
     </row>
     <row r="809" spans="8:11" x14ac:dyDescent="0.3">
@@ -6975,6 +7310,7 @@
     <row r="828" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H828" s="2"/>
       <c r="I828" s="1"/>
+      <c r="J828" s="2"/>
       <c r="K828" s="1"/>
     </row>
     <row r="829" spans="8:11" x14ac:dyDescent="0.3">
@@ -7058,6 +7394,7 @@
     <row r="842" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H842" s="2"/>
       <c r="I842" s="1"/>
+      <c r="J842" s="2"/>
       <c r="K842" s="1"/>
     </row>
     <row r="843" spans="8:11" x14ac:dyDescent="0.3">
@@ -7081,6 +7418,7 @@
     <row r="846" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H846" s="2"/>
       <c r="I846" s="1"/>
+      <c r="J846" s="2"/>
       <c r="K846" s="1"/>
     </row>
     <row r="847" spans="8:11" x14ac:dyDescent="0.3">
@@ -7092,6 +7430,7 @@
     <row r="848" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H848" s="2"/>
       <c r="I848" s="1"/>
+      <c r="J848" s="2"/>
       <c r="K848" s="1"/>
     </row>
     <row r="849" spans="8:11" x14ac:dyDescent="0.3">
@@ -7103,6 +7442,7 @@
     <row r="850" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H850" s="2"/>
       <c r="I850" s="1"/>
+      <c r="J850" s="2"/>
       <c r="K850" s="1"/>
     </row>
     <row r="851" spans="8:11" x14ac:dyDescent="0.3">
@@ -7150,6 +7490,7 @@
     <row r="858" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H858" s="2"/>
       <c r="I858" s="1"/>
+      <c r="J858" s="2"/>
       <c r="K858" s="1"/>
     </row>
     <row r="859" spans="8:11" x14ac:dyDescent="0.3">
@@ -7203,6 +7544,7 @@
     <row r="867" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H867" s="2"/>
       <c r="I867" s="1"/>
+      <c r="J867" s="2"/>
       <c r="K867" s="1"/>
     </row>
     <row r="868" spans="8:11" x14ac:dyDescent="0.3">
@@ -7375,6 +7717,7 @@
     <row r="896" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H896" s="2"/>
       <c r="I896" s="1"/>
+      <c r="J896" s="2"/>
       <c r="K896" s="1"/>
     </row>
     <row r="897" spans="8:11" x14ac:dyDescent="0.3">
@@ -7386,6 +7729,7 @@
     <row r="898" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H898" s="2"/>
       <c r="I898" s="1"/>
+      <c r="J898" s="2"/>
       <c r="K898" s="1"/>
     </row>
     <row r="899" spans="8:11" x14ac:dyDescent="0.3">
@@ -7463,6 +7807,7 @@
     <row r="911" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H911" s="2"/>
       <c r="I911" s="1"/>
+      <c r="J911" s="2"/>
       <c r="K911" s="1"/>
     </row>
     <row r="912" spans="8:11" x14ac:dyDescent="0.3">
@@ -7480,6 +7825,7 @@
     <row r="914" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H914" s="2"/>
       <c r="I914" s="1"/>
+      <c r="J914" s="2"/>
       <c r="K914" s="1"/>
     </row>
     <row r="915" spans="8:11" x14ac:dyDescent="0.3">
@@ -7527,6 +7873,7 @@
     <row r="922" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H922" s="2"/>
       <c r="I922" s="1"/>
+      <c r="J922" s="2"/>
       <c r="K922" s="1"/>
     </row>
     <row r="923" spans="8:11" x14ac:dyDescent="0.3">
@@ -7639,6 +7986,7 @@
     <row r="941" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H941" s="2"/>
       <c r="I941" s="1"/>
+      <c r="J941" s="2"/>
       <c r="K941" s="1"/>
     </row>
     <row r="942" spans="8:11" x14ac:dyDescent="0.3">
@@ -7698,6 +8046,7 @@
     <row r="951" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H951" s="2"/>
       <c r="I951" s="1"/>
+      <c r="J951" s="2"/>
       <c r="K951" s="1"/>
     </row>
     <row r="952" spans="8:11" x14ac:dyDescent="0.3">
@@ -7709,6 +8058,7 @@
     <row r="953" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H953" s="2"/>
       <c r="I953" s="1"/>
+      <c r="J953" s="2"/>
       <c r="K953" s="1"/>
     </row>
     <row r="954" spans="8:11" x14ac:dyDescent="0.3">
@@ -7780,6 +8130,7 @@
     <row r="965" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H965" s="2"/>
       <c r="I965" s="1"/>
+      <c r="J965" s="2"/>
       <c r="K965" s="1"/>
     </row>
     <row r="966" spans="8:11" x14ac:dyDescent="0.3">
@@ -7832,6 +8183,7 @@
     </row>
     <row r="974" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I974" s="1"/>
+      <c r="J974" s="2"/>
       <c r="K974" s="1"/>
     </row>
     <row r="975" spans="8:11" x14ac:dyDescent="0.3">
@@ -7908,11 +8260,13 @@
     <row r="987" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H987" s="2"/>
       <c r="I987" s="1"/>
+      <c r="J987" s="2"/>
       <c r="K987" s="1"/>
     </row>
     <row r="988" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H988" s="2"/>
       <c r="I988" s="1"/>
+      <c r="J988" s="2"/>
       <c r="K988" s="1"/>
     </row>
     <row r="989" spans="8:11" x14ac:dyDescent="0.3">
@@ -7972,6 +8326,7 @@
     <row r="998" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H998" s="2"/>
       <c r="I998" s="1"/>
+      <c r="J998" s="2"/>
       <c r="K998" s="1"/>
     </row>
     <row r="999" spans="8:11" x14ac:dyDescent="0.3">
@@ -7983,6 +8338,7 @@
     <row r="1000" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1000" s="2"/>
       <c r="I1000" s="1"/>
+      <c r="J1000" s="2"/>
       <c r="K1000" s="1"/>
     </row>
     <row r="1001" spans="8:11" x14ac:dyDescent="0.3">
@@ -7994,11 +8350,13 @@
     <row r="1002" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1002" s="2"/>
       <c r="I1002" s="1"/>
+      <c r="J1002" s="2"/>
       <c r="K1002" s="1"/>
     </row>
     <row r="1003" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1003" s="2"/>
       <c r="I1003" s="1"/>
+      <c r="J1003" s="2"/>
       <c r="K1003" s="1"/>
     </row>
     <row r="1004" spans="8:11" x14ac:dyDescent="0.3">
@@ -8052,6 +8410,7 @@
     <row r="1012" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1012" s="2"/>
       <c r="I1012" s="1"/>
+      <c r="J1012" s="2"/>
       <c r="K1012" s="1"/>
     </row>
     <row r="1013" spans="8:11" x14ac:dyDescent="0.3">
@@ -8068,6 +8427,7 @@
     </row>
     <row r="1015" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1015" s="1"/>
+      <c r="J1015" s="2"/>
       <c r="K1015" s="1"/>
     </row>
     <row r="1016" spans="8:11" x14ac:dyDescent="0.3">
@@ -8091,6 +8451,7 @@
     <row r="1019" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1019" s="2"/>
       <c r="I1019" s="1"/>
+      <c r="J1019" s="2"/>
       <c r="K1019" s="1"/>
     </row>
     <row r="1020" spans="8:11" x14ac:dyDescent="0.3">
@@ -8108,6 +8469,7 @@
     <row r="1022" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1022" s="2"/>
       <c r="I1022" s="1"/>
+      <c r="J1022" s="2"/>
       <c r="K1022" s="1"/>
     </row>
     <row r="1023" spans="8:11" x14ac:dyDescent="0.3">
@@ -8154,11 +8516,13 @@
     </row>
     <row r="1030" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1030" s="1"/>
+      <c r="J1030" s="2"/>
       <c r="K1030" s="1"/>
     </row>
     <row r="1031" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1031" s="2"/>
       <c r="I1031" s="1"/>
+      <c r="J1031" s="2"/>
       <c r="K1031" s="1"/>
     </row>
     <row r="1032" spans="8:11" x14ac:dyDescent="0.3">
@@ -8200,11 +8564,13 @@
     <row r="1038" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1038" s="2"/>
       <c r="I1038" s="1"/>
+      <c r="J1038" s="2"/>
       <c r="K1038" s="1"/>
     </row>
     <row r="1039" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1039" s="2"/>
       <c r="I1039" s="1"/>
+      <c r="J1039" s="2"/>
       <c r="K1039" s="1"/>
     </row>
     <row r="1040" spans="8:11" x14ac:dyDescent="0.3">
@@ -8222,6 +8588,7 @@
     <row r="1042" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1042" s="2"/>
       <c r="I1042" s="1"/>
+      <c r="J1042" s="2"/>
       <c r="K1042" s="1"/>
     </row>
     <row r="1043" spans="8:11" x14ac:dyDescent="0.3">
@@ -8233,6 +8600,7 @@
     <row r="1044" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1044" s="2"/>
       <c r="I1044" s="1"/>
+      <c r="J1044" s="2"/>
       <c r="K1044" s="1"/>
     </row>
     <row r="1045" spans="8:11" x14ac:dyDescent="0.3">
@@ -8244,6 +8612,7 @@
     <row r="1046" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1046" s="2"/>
       <c r="I1046" s="1"/>
+      <c r="J1046" s="2"/>
       <c r="K1046" s="1"/>
     </row>
     <row r="1047" spans="8:11" x14ac:dyDescent="0.3">
@@ -8261,6 +8630,7 @@
     <row r="1049" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1049" s="2"/>
       <c r="I1049" s="1"/>
+      <c r="J1049" s="2"/>
       <c r="K1049" s="1"/>
     </row>
     <row r="1050" spans="8:11" x14ac:dyDescent="0.3">
@@ -8338,6 +8708,7 @@
     <row r="1062" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1062" s="2"/>
       <c r="I1062" s="1"/>
+      <c r="J1062" s="2"/>
       <c r="K1062" s="1"/>
     </row>
     <row r="1063" spans="8:11" x14ac:dyDescent="0.3">
@@ -8367,6 +8738,7 @@
     <row r="1067" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1067" s="2"/>
       <c r="I1067" s="1"/>
+      <c r="J1067" s="2"/>
       <c r="K1067" s="1"/>
     </row>
     <row r="1068" spans="8:11" x14ac:dyDescent="0.3">
@@ -8378,16 +8750,19 @@
     <row r="1069" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1069" s="2"/>
       <c r="I1069" s="1"/>
+      <c r="J1069" s="2"/>
       <c r="K1069" s="1"/>
     </row>
     <row r="1070" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1070" s="2"/>
       <c r="I1070" s="1"/>
+      <c r="J1070" s="2"/>
       <c r="K1070" s="1"/>
     </row>
     <row r="1071" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1071" s="2"/>
       <c r="I1071" s="1"/>
+      <c r="J1071" s="2"/>
       <c r="K1071" s="1"/>
     </row>
     <row r="1072" spans="8:11" x14ac:dyDescent="0.3">
@@ -8399,16 +8774,19 @@
     <row r="1073" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1073" s="2"/>
       <c r="I1073" s="1"/>
+      <c r="J1073" s="2"/>
       <c r="K1073" s="1"/>
     </row>
     <row r="1074" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1074" s="2"/>
       <c r="I1074" s="1"/>
+      <c r="J1074" s="2"/>
       <c r="K1074" s="1"/>
     </row>
     <row r="1075" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1075" s="2"/>
       <c r="I1075" s="1"/>
+      <c r="J1075" s="2"/>
       <c r="K1075" s="1"/>
     </row>
     <row r="1076" spans="8:11" x14ac:dyDescent="0.3">
@@ -8420,11 +8798,13 @@
     <row r="1077" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1077" s="2"/>
       <c r="I1077" s="1"/>
+      <c r="J1077" s="2"/>
       <c r="K1077" s="1"/>
     </row>
     <row r="1078" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1078" s="2"/>
       <c r="I1078" s="1"/>
+      <c r="J1078" s="2"/>
       <c r="K1078" s="1"/>
     </row>
     <row r="1079" spans="8:11" x14ac:dyDescent="0.3">
@@ -8448,6 +8828,7 @@
     <row r="1082" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1082" s="2"/>
       <c r="I1082" s="1"/>
+      <c r="J1082" s="2"/>
       <c r="K1082" s="1"/>
     </row>
     <row r="1083" spans="8:11" x14ac:dyDescent="0.3">
@@ -8489,6 +8870,7 @@
     <row r="1089" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1089" s="2"/>
       <c r="I1089" s="1"/>
+      <c r="J1089" s="2"/>
       <c r="K1089" s="1"/>
     </row>
     <row r="1090" spans="8:11" x14ac:dyDescent="0.3">
@@ -8518,21 +8900,25 @@
     <row r="1094" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1094" s="2"/>
       <c r="I1094" s="1"/>
+      <c r="J1094" s="2"/>
       <c r="K1094" s="1"/>
     </row>
     <row r="1095" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1095" s="2"/>
       <c r="I1095" s="1"/>
+      <c r="J1095" s="2"/>
       <c r="K1095" s="1"/>
     </row>
     <row r="1096" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1096" s="2"/>
       <c r="I1096" s="1"/>
+      <c r="J1096" s="2"/>
       <c r="K1096" s="1"/>
     </row>
     <row r="1097" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1097" s="2"/>
       <c r="I1097" s="1"/>
+      <c r="J1097" s="2"/>
       <c r="K1097" s="1"/>
     </row>
     <row r="1098" spans="8:11" x14ac:dyDescent="0.3">
@@ -8544,6 +8930,7 @@
     <row r="1099" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1099" s="2"/>
       <c r="I1099" s="1"/>
+      <c r="J1099" s="2"/>
       <c r="K1099" s="1"/>
     </row>
     <row r="1100" spans="8:11" x14ac:dyDescent="0.3">
@@ -8561,6 +8948,7 @@
     <row r="1102" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1102" s="2"/>
       <c r="I1102" s="1"/>
+      <c r="J1102" s="2"/>
       <c r="K1102" s="1"/>
     </row>
     <row r="1103" spans="8:11" x14ac:dyDescent="0.3">
@@ -8600,11 +8988,13 @@
     <row r="1109" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1109" s="2"/>
       <c r="I1109" s="1"/>
+      <c r="J1109" s="2"/>
       <c r="K1109" s="1"/>
     </row>
     <row r="1110" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1110" s="2"/>
       <c r="I1110" s="1"/>
+      <c r="J1110" s="2"/>
       <c r="K1110" s="1"/>
     </row>
     <row r="1111" spans="8:11" x14ac:dyDescent="0.3">
@@ -8652,6 +9042,7 @@
     <row r="1118" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1118" s="2"/>
       <c r="I1118" s="1"/>
+      <c r="J1118" s="2"/>
       <c r="K1118" s="1"/>
     </row>
     <row r="1119" spans="8:11" x14ac:dyDescent="0.3">
@@ -8681,6 +9072,7 @@
     <row r="1123" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1123" s="2"/>
       <c r="I1123" s="1"/>
+      <c r="J1123" s="2"/>
       <c r="K1123" s="1"/>
     </row>
     <row r="1124" spans="8:11" x14ac:dyDescent="0.3">
@@ -8757,6 +9149,7 @@
     <row r="1136" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1136" s="2"/>
       <c r="I1136" s="1"/>
+      <c r="J1136" s="2"/>
       <c r="K1136" s="1"/>
     </row>
     <row r="1137" spans="8:11" x14ac:dyDescent="0.3">
@@ -8803,6 +9196,7 @@
     <row r="1144" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1144" s="2"/>
       <c r="I1144" s="1"/>
+      <c r="J1144" s="2"/>
       <c r="K1144" s="1"/>
     </row>
     <row r="1145" spans="8:11" x14ac:dyDescent="0.3">
@@ -8838,11 +9232,13 @@
     <row r="1150" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1150" s="2"/>
       <c r="I1150" s="1"/>
+      <c r="J1150" s="2"/>
       <c r="K1150" s="1"/>
     </row>
     <row r="1151" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1151" s="2"/>
       <c r="I1151" s="1"/>
+      <c r="J1151" s="2"/>
       <c r="K1151" s="1"/>
     </row>
     <row r="1152" spans="8:11" x14ac:dyDescent="0.3">
@@ -8859,6 +9255,7 @@
     <row r="1154" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1154" s="2"/>
       <c r="I1154" s="1"/>
+      <c r="J1154" s="2"/>
       <c r="K1154" s="1"/>
     </row>
     <row r="1155" spans="8:11" x14ac:dyDescent="0.3">
@@ -8869,6 +9266,7 @@
     <row r="1156" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1156" s="2"/>
       <c r="I1156" s="1"/>
+      <c r="J1156" s="2"/>
       <c r="K1156" s="1"/>
     </row>
     <row r="1157" spans="8:11" x14ac:dyDescent="0.3">
@@ -8904,6 +9302,7 @@
     <row r="1162" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1162" s="2"/>
       <c r="I1162" s="1"/>
+      <c r="J1162" s="2"/>
       <c r="K1162" s="1"/>
     </row>
     <row r="1163" spans="8:11" x14ac:dyDescent="0.3">
@@ -8915,6 +9314,7 @@
     <row r="1164" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1164" s="2"/>
       <c r="I1164" s="1"/>
+      <c r="J1164" s="2"/>
       <c r="K1164" s="1"/>
     </row>
     <row r="1165" spans="8:11" x14ac:dyDescent="0.3">
@@ -8926,6 +9326,7 @@
     <row r="1166" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1166" s="2"/>
       <c r="I1166" s="1"/>
+      <c r="J1166" s="2"/>
       <c r="K1166" s="1"/>
     </row>
     <row r="1167" spans="8:11" x14ac:dyDescent="0.3">
@@ -8937,6 +9338,7 @@
     <row r="1168" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1168" s="2"/>
       <c r="I1168" s="1"/>
+      <c r="J1168" s="2"/>
       <c r="K1168" s="1"/>
     </row>
     <row r="1169" spans="8:11" x14ac:dyDescent="0.3">
@@ -8948,6 +9350,7 @@
     <row r="1170" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1170" s="2"/>
       <c r="I1170" s="1"/>
+      <c r="J1170" s="2"/>
       <c r="K1170" s="1"/>
     </row>
     <row r="1171" spans="8:11" x14ac:dyDescent="0.3">
@@ -8989,6 +9392,7 @@
     <row r="1177" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1177" s="2"/>
       <c r="I1177" s="1"/>
+      <c r="J1177" s="2"/>
       <c r="K1177" s="1"/>
     </row>
     <row r="1178" spans="8:11" x14ac:dyDescent="0.3">
@@ -9006,6 +9410,7 @@
     <row r="1180" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1180" s="2"/>
       <c r="I1180" s="1"/>
+      <c r="J1180" s="2"/>
       <c r="K1180" s="1"/>
     </row>
     <row r="1181" spans="8:11" x14ac:dyDescent="0.3">
@@ -9023,6 +9428,7 @@
     <row r="1183" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1183" s="2"/>
       <c r="I1183" s="1"/>
+      <c r="J1183" s="2"/>
       <c r="K1183" s="1"/>
     </row>
     <row r="1184" spans="8:11" x14ac:dyDescent="0.3">
@@ -9064,6 +9470,7 @@
     <row r="1190" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1190" s="2"/>
       <c r="I1190" s="1"/>
+      <c r="J1190" s="2"/>
       <c r="K1190" s="1"/>
     </row>
     <row r="1191" spans="8:11" x14ac:dyDescent="0.3">
@@ -9087,6 +9494,7 @@
     <row r="1194" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1194" s="2"/>
       <c r="I1194" s="1"/>
+      <c r="J1194" s="2"/>
       <c r="K1194" s="1"/>
     </row>
     <row r="1195" spans="8:11" x14ac:dyDescent="0.3">
@@ -9133,6 +9541,7 @@
     <row r="1202" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1202" s="2"/>
       <c r="I1202" s="1"/>
+      <c r="J1202" s="2"/>
       <c r="K1202" s="1"/>
     </row>
     <row r="1203" spans="8:11" x14ac:dyDescent="0.3">
@@ -9168,6 +9577,7 @@
     <row r="1208" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1208" s="2"/>
       <c r="I1208" s="1"/>
+      <c r="J1208" s="2"/>
       <c r="K1208" s="1"/>
     </row>
     <row r="1209" spans="8:11" x14ac:dyDescent="0.3">
@@ -9191,6 +9601,7 @@
     <row r="1212" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1212" s="2"/>
       <c r="I1212" s="1"/>
+      <c r="J1212" s="2"/>
       <c r="K1212" s="1"/>
     </row>
     <row r="1213" spans="8:11" x14ac:dyDescent="0.3">
@@ -9231,6 +9642,7 @@
     <row r="1219" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1219" s="2"/>
       <c r="I1219" s="1"/>
+      <c r="J1219" s="2"/>
       <c r="K1219" s="1"/>
     </row>
     <row r="1220" spans="8:11" x14ac:dyDescent="0.3">
@@ -9248,11 +9660,13 @@
     <row r="1222" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1222" s="2"/>
       <c r="I1222" s="1"/>
+      <c r="J1222" s="2"/>
       <c r="K1222" s="1"/>
     </row>
     <row r="1223" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1223" s="2"/>
       <c r="I1223" s="1"/>
+      <c r="J1223" s="2"/>
       <c r="K1223" s="1"/>
     </row>
     <row r="1224" spans="8:11" x14ac:dyDescent="0.3">
@@ -9311,6 +9725,7 @@
     <row r="1233" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1233" s="2"/>
       <c r="I1233" s="1"/>
+      <c r="J1233" s="2"/>
       <c r="K1233" s="1"/>
     </row>
     <row r="1234" spans="8:11" x14ac:dyDescent="0.3">
@@ -9327,6 +9742,7 @@
     <row r="1236" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1236" s="2"/>
       <c r="I1236" s="1"/>
+      <c r="J1236" s="2"/>
       <c r="K1236" s="1"/>
     </row>
     <row r="1237" spans="8:11" x14ac:dyDescent="0.3">
@@ -9338,6 +9754,7 @@
     <row r="1238" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1238" s="2"/>
       <c r="I1238" s="1"/>
+      <c r="J1238" s="2"/>
       <c r="K1238" s="1"/>
     </row>
     <row r="1239" spans="8:11" x14ac:dyDescent="0.3">
@@ -9349,11 +9766,13 @@
     <row r="1240" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1240" s="2"/>
       <c r="I1240" s="1"/>
+      <c r="J1240" s="2"/>
       <c r="K1240" s="1"/>
     </row>
     <row r="1241" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1241" s="2"/>
       <c r="I1241" s="1"/>
+      <c r="J1241" s="2"/>
       <c r="K1241" s="1"/>
     </row>
     <row r="1242" spans="8:11" x14ac:dyDescent="0.3">
@@ -9389,6 +9808,7 @@
     <row r="1247" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1247" s="2"/>
       <c r="I1247" s="1"/>
+      <c r="J1247" s="2"/>
       <c r="K1247" s="1"/>
     </row>
     <row r="1248" spans="8:11" x14ac:dyDescent="0.3">
@@ -9441,6 +9861,7 @@
     <row r="1256" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1256" s="2"/>
       <c r="I1256" s="1"/>
+      <c r="J1256" s="2"/>
       <c r="K1256" s="1"/>
     </row>
     <row r="1257" spans="8:11" x14ac:dyDescent="0.3">
@@ -9451,6 +9872,7 @@
     </row>
     <row r="1258" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1258" s="1"/>
+      <c r="J1258" s="2"/>
       <c r="K1258" s="1"/>
     </row>
     <row r="1259" spans="8:11" x14ac:dyDescent="0.3">
@@ -9466,6 +9888,7 @@
     </row>
     <row r="1261" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1261" s="1"/>
+      <c r="J1261" s="2"/>
       <c r="K1261" s="1"/>
     </row>
     <row r="1262" spans="8:11" x14ac:dyDescent="0.3">
@@ -9489,16 +9912,19 @@
     <row r="1265" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1265" s="2"/>
       <c r="I1265" s="1"/>
+      <c r="J1265" s="2"/>
       <c r="K1265" s="1"/>
     </row>
     <row r="1266" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1266" s="2"/>
       <c r="I1266" s="1"/>
+      <c r="J1266" s="2"/>
       <c r="K1266" s="1"/>
     </row>
     <row r="1267" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1267" s="2"/>
       <c r="I1267" s="1"/>
+      <c r="J1267" s="2"/>
       <c r="K1267" s="1"/>
     </row>
     <row r="1268" spans="8:11" x14ac:dyDescent="0.3">
@@ -9569,6 +9995,7 @@
     <row r="1279" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1279" s="2"/>
       <c r="I1279" s="1"/>
+      <c r="J1279" s="2"/>
       <c r="K1279" s="1"/>
     </row>
     <row r="1280" spans="8:11" x14ac:dyDescent="0.3">
@@ -9580,6 +10007,7 @@
     <row r="1281" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1281" s="2"/>
       <c r="I1281" s="1"/>
+      <c r="J1281" s="2"/>
       <c r="K1281" s="1"/>
     </row>
     <row r="1282" spans="8:11" x14ac:dyDescent="0.3">
@@ -9680,6 +10108,8 @@
     <row r="1298" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1298" s="2"/>
       <c r="I1298" s="1"/>
+      <c r="J1298" s="2"/>
+      <c r="K1298" s="1"/>
     </row>
     <row r="1299" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1299" s="2"/>
@@ -9736,6 +10166,7 @@
     <row r="1308" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1308" s="2"/>
       <c r="I1308" s="1"/>
+      <c r="J1308" s="2"/>
       <c r="K1308" s="1"/>
     </row>
     <row r="1309" spans="8:11" x14ac:dyDescent="0.3">
@@ -9759,6 +10190,7 @@
     <row r="1312" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1312" s="2"/>
       <c r="I1312" s="1"/>
+      <c r="J1312" s="2"/>
       <c r="K1312" s="1"/>
     </row>
     <row r="1313" spans="8:11" x14ac:dyDescent="0.3">
@@ -9883,6 +10315,7 @@
     <row r="1333" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1333" s="2"/>
       <c r="I1333" s="1"/>
+      <c r="J1333" s="2"/>
       <c r="K1333" s="1"/>
     </row>
     <row r="1334" spans="8:11" x14ac:dyDescent="0.3">
@@ -10041,6 +10474,7 @@
     <row r="1360" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1360" s="2"/>
       <c r="I1360" s="1"/>
+      <c r="J1360" s="2"/>
       <c r="K1360" s="1"/>
     </row>
     <row r="1361" spans="8:11" x14ac:dyDescent="0.3">
@@ -10058,6 +10492,7 @@
     <row r="1363" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1363" s="2"/>
       <c r="I1363" s="1"/>
+      <c r="J1363" s="2"/>
       <c r="K1363" s="1"/>
     </row>
     <row r="1364" spans="8:11" x14ac:dyDescent="0.3">
@@ -10098,6 +10533,7 @@
     <row r="1370" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1370" s="2"/>
       <c r="I1370" s="1"/>
+      <c r="J1370" s="2"/>
       <c r="K1370" s="1"/>
     </row>
     <row r="1371" spans="8:11" x14ac:dyDescent="0.3">
@@ -10430,6 +10866,7 @@
     <row r="1427" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1427" s="2"/>
       <c r="I1427" s="1"/>
+      <c r="J1427" s="2"/>
       <c r="K1427" s="1"/>
     </row>
     <row r="1428" spans="8:11" x14ac:dyDescent="0.3">
@@ -10518,6 +10955,7 @@
     <row r="1442" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1442" s="2"/>
       <c r="I1442" s="1"/>
+      <c r="J1442" s="2"/>
       <c r="K1442" s="1"/>
     </row>
     <row r="1443" spans="8:11" x14ac:dyDescent="0.3">
@@ -10611,6 +11049,7 @@
     <row r="1458" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1458" s="2"/>
       <c r="I1458" s="1"/>
+      <c r="J1458" s="2"/>
       <c r="K1458" s="1"/>
     </row>
     <row r="1459" spans="8:11" x14ac:dyDescent="0.3">
@@ -10670,11 +11109,13 @@
     <row r="1468" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1468" s="2"/>
       <c r="I1468" s="1"/>
+      <c r="J1468" s="2"/>
       <c r="K1468" s="1"/>
     </row>
     <row r="1469" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1469" s="2"/>
       <c r="I1469" s="1"/>
+      <c r="J1469" s="2"/>
       <c r="K1469" s="1"/>
     </row>
     <row r="1470" spans="8:11" x14ac:dyDescent="0.3">
@@ -10726,6 +11167,7 @@
     </row>
     <row r="1478" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1478" s="1"/>
+      <c r="J1478" s="2"/>
       <c r="K1478" s="1"/>
     </row>
     <row r="1479" spans="8:11" x14ac:dyDescent="0.3">
@@ -10767,6 +11209,7 @@
     <row r="1485" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1485" s="2"/>
       <c r="I1485" s="1"/>
+      <c r="J1485" s="2"/>
       <c r="K1485" s="1"/>
     </row>
     <row r="1486" spans="8:11" x14ac:dyDescent="0.3">
@@ -10811,6 +11254,7 @@
     </row>
     <row r="1493" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1493" s="1"/>
+      <c r="J1493" s="2"/>
       <c r="K1493" s="1"/>
     </row>
     <row r="1494" spans="8:11" x14ac:dyDescent="0.3">
@@ -10857,11 +11301,13 @@
     <row r="1501" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1501" s="2"/>
       <c r="I1501" s="1"/>
+      <c r="J1501" s="2"/>
       <c r="K1501" s="1"/>
     </row>
     <row r="1502" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1502" s="2"/>
       <c r="I1502" s="1"/>
+      <c r="J1502" s="2"/>
       <c r="K1502" s="1"/>
     </row>
     <row r="1503" spans="8:11" x14ac:dyDescent="0.3">
@@ -11059,6 +11505,7 @@
     <row r="1535" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1535" s="2"/>
       <c r="I1535" s="1"/>
+      <c r="J1535" s="2"/>
       <c r="K1535" s="1"/>
     </row>
     <row r="1536" spans="8:11" x14ac:dyDescent="0.3">
@@ -11088,6 +11535,8 @@
     <row r="1540" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1540" s="2"/>
       <c r="I1540" s="1"/>
+      <c r="J1540" s="2"/>
+      <c r="K1540" s="1"/>
     </row>
     <row r="1541" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1541" s="1"/>
@@ -11103,6 +11552,7 @@
     <row r="1543" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1543" s="2"/>
       <c r="I1543" s="1"/>
+      <c r="J1543" s="2"/>
       <c r="K1543" s="1"/>
     </row>
     <row r="1544" spans="8:11" x14ac:dyDescent="0.3">
@@ -11162,6 +11612,7 @@
     <row r="1553" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1553" s="2"/>
       <c r="I1553" s="1"/>
+      <c r="J1553" s="2"/>
       <c r="K1553" s="1"/>
     </row>
     <row r="1554" spans="8:11" x14ac:dyDescent="0.3">
@@ -11233,6 +11684,7 @@
     <row r="1565" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1565" s="2"/>
       <c r="I1565" s="1"/>
+      <c r="J1565" s="2"/>
       <c r="K1565" s="1"/>
     </row>
     <row r="1566" spans="8:11" x14ac:dyDescent="0.3">
@@ -11274,6 +11726,7 @@
     <row r="1572" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1572" s="2"/>
       <c r="I1572" s="1"/>
+      <c r="J1572" s="2"/>
       <c r="K1572" s="1"/>
     </row>
     <row r="1573" spans="8:11" x14ac:dyDescent="0.3">
@@ -11392,6 +11845,7 @@
     <row r="1592" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1592" s="2"/>
       <c r="I1592" s="1"/>
+      <c r="J1592" s="2"/>
       <c r="K1592" s="1"/>
     </row>
     <row r="1593" spans="8:11" x14ac:dyDescent="0.3">
@@ -11456,6 +11910,7 @@
     <row r="1603" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1603" s="2"/>
       <c r="I1603" s="1"/>
+      <c r="J1603" s="2"/>
       <c r="K1603" s="1"/>
     </row>
     <row r="1604" spans="8:11" x14ac:dyDescent="0.3">
@@ -11580,6 +12035,7 @@
     <row r="1624" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1624" s="2"/>
       <c r="I1624" s="1"/>
+      <c r="J1624" s="2"/>
       <c r="K1624" s="1"/>
     </row>
     <row r="1625" spans="8:11" x14ac:dyDescent="0.3">
@@ -11806,6 +12262,7 @@
     <row r="1662" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1662" s="2"/>
       <c r="I1662" s="1"/>
+      <c r="J1662" s="2"/>
       <c r="K1662" s="1"/>
     </row>
     <row r="1663" spans="8:11" x14ac:dyDescent="0.3">
@@ -11923,6 +12380,7 @@
     <row r="1682" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1682" s="2"/>
       <c r="I1682" s="1"/>
+      <c r="J1682" s="2"/>
       <c r="K1682" s="1"/>
     </row>
     <row r="1683" spans="8:11" x14ac:dyDescent="0.3">
@@ -12006,6 +12464,7 @@
     <row r="1696" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1696" s="2"/>
       <c r="I1696" s="1"/>
+      <c r="J1696" s="2"/>
       <c r="K1696" s="1"/>
     </row>
     <row r="1697" spans="8:11" x14ac:dyDescent="0.3">
@@ -12065,6 +12524,7 @@
     <row r="1706" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1706" s="2"/>
       <c r="I1706" s="1"/>
+      <c r="J1706" s="2"/>
       <c r="K1706" s="1"/>
     </row>
     <row r="1707" spans="8:11" x14ac:dyDescent="0.3">
@@ -12088,6 +12548,7 @@
     <row r="1710" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1710" s="2"/>
       <c r="I1710" s="1"/>
+      <c r="J1710" s="2"/>
       <c r="K1710" s="1"/>
     </row>
     <row r="1711" spans="8:11" x14ac:dyDescent="0.3">
@@ -12135,6 +12596,7 @@
     <row r="1718" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1718" s="2"/>
       <c r="I1718" s="1"/>
+      <c r="J1718" s="2"/>
       <c r="K1718" s="1"/>
     </row>
     <row r="1719" spans="8:11" x14ac:dyDescent="0.3">
@@ -12194,6 +12656,7 @@
     <row r="1728" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1728" s="2"/>
       <c r="I1728" s="1"/>
+      <c r="J1728" s="2"/>
       <c r="K1728" s="1"/>
     </row>
     <row r="1729" spans="8:11" x14ac:dyDescent="0.3">
@@ -12217,6 +12680,7 @@
     <row r="1732" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1732" s="2"/>
       <c r="I1732" s="1"/>
+      <c r="J1732" s="2"/>
       <c r="K1732" s="1"/>
     </row>
     <row r="1733" spans="8:11" x14ac:dyDescent="0.3">
@@ -12234,6 +12698,7 @@
     <row r="1735" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1735" s="2"/>
       <c r="I1735" s="1"/>
+      <c r="J1735" s="2"/>
       <c r="K1735" s="1"/>
     </row>
     <row r="1736" spans="8:11" x14ac:dyDescent="0.3">
@@ -12317,6 +12782,7 @@
     <row r="1749" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1749" s="2"/>
       <c r="I1749" s="1"/>
+      <c r="J1749" s="2"/>
       <c r="K1749" s="1"/>
     </row>
     <row r="1750" spans="8:11" x14ac:dyDescent="0.3">
@@ -12508,6 +12974,7 @@
     <row r="1781" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1781" s="2"/>
       <c r="I1781" s="1"/>
+      <c r="J1781" s="2"/>
       <c r="K1781" s="1"/>
     </row>
     <row r="1782" spans="8:11" x14ac:dyDescent="0.3">
@@ -40364,6 +40831,7 @@
       <c r="K6920" s="1"/>
     </row>
     <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6921" s="2"/>
       <c r="K6921" s="1"/>
     </row>
     <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
@@ -40371,6 +40839,7 @@
       <c r="K6922" s="1"/>
     </row>
     <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6923" s="2"/>
       <c r="K6923" s="1"/>
     </row>
     <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
@@ -40378,6 +40847,7 @@
       <c r="K6924" s="1"/>
     </row>
     <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6925" s="2"/>
       <c r="K6925" s="1"/>
     </row>
     <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
@@ -40393,6 +40863,7 @@
       <c r="K6928" s="1"/>
     </row>
     <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6929" s="2"/>
       <c r="K6929" s="1"/>
     </row>
     <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
@@ -40402,6 +40873,7 @@
       <c r="K6931" s="1"/>
     </row>
     <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6932" s="2"/>
       <c r="K6932" s="1"/>
     </row>
     <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
@@ -40409,9 +40881,15 @@
       <c r="K6933" s="1"/>
     </row>
     <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6934" s="2"/>
       <c r="K6934" s="1"/>
     </row>
+    <row r="6935" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6935" s="2"/>
+      <c r="K6935" s="1"/>
+    </row>
     <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6936" s="2"/>
       <c r="K6936" s="1"/>
     </row>
     <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
@@ -40419,12 +40897,15 @@
       <c r="K6937" s="1"/>
     </row>
     <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6938" s="2"/>
       <c r="K6938" s="1"/>
     </row>
     <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6939" s="2"/>
       <c r="K6939" s="1"/>
     </row>
     <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6940" s="2"/>
       <c r="K6940" s="1"/>
     </row>
     <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
@@ -40432,12 +40913,15 @@
       <c r="K6941" s="1"/>
     </row>
     <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6942" s="2"/>
       <c r="K6942" s="1"/>
     </row>
     <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6943" s="2"/>
       <c r="K6943" s="1"/>
     </row>
     <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6944" s="2"/>
       <c r="K6944" s="1"/>
     </row>
     <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
@@ -40449,9 +40933,11 @@
       <c r="K6946" s="1"/>
     </row>
     <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6947" s="2"/>
       <c r="K6947" s="1"/>
     </row>
     <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6948" s="2"/>
       <c r="K6948" s="1"/>
     </row>
     <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
@@ -40466,6 +40952,7 @@
       <c r="K6951" s="1"/>
     </row>
     <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6952" s="2"/>
       <c r="K6952" s="1"/>
     </row>
     <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
@@ -40492,6 +40979,7 @@
       <c r="K6958" s="1"/>
     </row>
     <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6959" s="2"/>
       <c r="K6959" s="1"/>
     </row>
     <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
@@ -40502,7 +40990,12 @@
       <c r="J6961" s="2"/>
       <c r="K6961" s="1"/>
     </row>
+    <row r="6962" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6962" s="2"/>
+      <c r="K6962" s="1"/>
+    </row>
     <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6963" s="2"/>
       <c r="K6963" s="1"/>
     </row>
     <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
@@ -40510,6 +41003,7 @@
       <c r="K6964" s="1"/>
     </row>
     <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6965" s="2"/>
       <c r="K6965" s="1"/>
     </row>
     <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
@@ -40521,6 +41015,7 @@
       <c r="K6967" s="1"/>
     </row>
     <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6968" s="2"/>
       <c r="K6968" s="1"/>
     </row>
     <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
@@ -40528,6 +41023,7 @@
       <c r="K6969" s="1"/>
     </row>
     <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6970" s="2"/>
       <c r="K6970" s="1"/>
     </row>
     <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
@@ -40542,13 +41038,19 @@
       <c r="K6973" s="1"/>
     </row>
     <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6974" s="2"/>
       <c r="K6974" s="1"/>
     </row>
     <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J6975" s="2"/>
       <c r="K6975" s="1"/>
     </row>
+    <row r="6976" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6976" s="2"/>
+      <c r="K6976" s="1"/>
+    </row>
     <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6977" s="2"/>
       <c r="K6977" s="1"/>
     </row>
     <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
@@ -40559,15 +41061,18 @@
       <c r="K6979" s="1"/>
     </row>
     <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6980" s="2"/>
       <c r="K6980" s="1"/>
     </row>
     <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6981" s="2"/>
       <c r="K6981" s="1"/>
     </row>
     <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K6982" s="1"/>
     </row>
     <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6983" s="2"/>
       <c r="K6983" s="1"/>
     </row>
     <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
@@ -40583,6 +41088,7 @@
       <c r="K6986" s="1"/>
     </row>
     <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6987" s="2"/>
       <c r="K6987" s="1"/>
     </row>
     <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
@@ -40601,6 +41107,7 @@
       <c r="K6991" s="1"/>
     </row>
     <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6992" s="2"/>
       <c r="K6992" s="1"/>
     </row>
     <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
@@ -40612,6 +41119,7 @@
       <c r="K6994" s="1"/>
     </row>
     <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6995" s="2"/>
       <c r="K6995" s="1"/>
     </row>
     <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
@@ -40629,18 +41137,23 @@
       <c r="K6999" s="1"/>
     </row>
     <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7000" s="2"/>
       <c r="K7000" s="1"/>
     </row>
     <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7001" s="2"/>
       <c r="K7001" s="1"/>
     </row>
     <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7002" s="2"/>
       <c r="K7002" s="1"/>
     </row>
     <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7003" s="2"/>
       <c r="K7003" s="1"/>
     </row>
     <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7004" s="2"/>
       <c r="K7004" s="1"/>
     </row>
     <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
@@ -40669,6 +41182,7 @@
       <c r="K7012" s="1"/>
     </row>
     <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7014" s="2"/>
       <c r="K7014" s="1"/>
     </row>
     <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
@@ -40676,9 +41190,11 @@
       <c r="K7015" s="1"/>
     </row>
     <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7016" s="2"/>
       <c r="K7016" s="1"/>
     </row>
     <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7017" s="2"/>
       <c r="K7017" s="1"/>
     </row>
     <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
@@ -40701,12 +41217,15 @@
       <c r="K7022" s="1"/>
     </row>
     <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7023" s="2"/>
       <c r="K7023" s="1"/>
     </row>
     <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7024" s="2"/>
       <c r="K7024" s="1"/>
     </row>
     <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7025" s="2"/>
       <c r="K7025" s="1"/>
     </row>
     <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
@@ -40721,9 +41240,11 @@
       <c r="K7028" s="1"/>
     </row>
     <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7030" s="2"/>
       <c r="K7030" s="1"/>
     </row>
     <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7031" s="2"/>
       <c r="K7031" s="1"/>
     </row>
     <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
@@ -40739,12 +41260,14 @@
       <c r="K7034" s="1"/>
     </row>
     <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7035" s="2"/>
       <c r="K7035" s="1"/>
     </row>
     <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7036" s="1"/>
     </row>
     <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7037" s="2"/>
       <c r="K7037" s="1"/>
     </row>
     <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
@@ -40765,6 +41288,7 @@
       <c r="K7042" s="1"/>
     </row>
     <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7043" s="2"/>
       <c r="K7043" s="1"/>
     </row>
     <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
@@ -40776,9 +41300,11 @@
       <c r="K7045" s="1"/>
     </row>
     <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7046" s="2"/>
       <c r="K7046" s="1"/>
     </row>
     <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7047" s="2"/>
       <c r="K7047" s="1"/>
     </row>
     <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
@@ -40790,6 +41316,7 @@
       <c r="K7049" s="1"/>
     </row>
     <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7050" s="2"/>
       <c r="K7050" s="1"/>
     </row>
     <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
@@ -40829,9 +41356,11 @@
       <c r="K7059" s="1"/>
     </row>
     <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7060" s="2"/>
       <c r="K7060" s="1"/>
     </row>
     <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7061" s="2"/>
       <c r="K7061" s="1"/>
     </row>
     <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
@@ -40839,9 +41368,11 @@
       <c r="K7062" s="1"/>
     </row>
     <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7063" s="2"/>
       <c r="K7063" s="1"/>
     </row>
     <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7064" s="2"/>
       <c r="K7064" s="1"/>
     </row>
     <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
@@ -40852,6 +41383,7 @@
       <c r="K7066" s="1"/>
     </row>
     <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7067" s="2"/>
       <c r="K7067" s="1"/>
     </row>
     <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
@@ -40859,18 +41391,26 @@
       <c r="K7068" s="1"/>
     </row>
     <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7069" s="2"/>
       <c r="K7069" s="1"/>
     </row>
+    <row r="7070" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7070" s="2"/>
+      <c r="K7070" s="1"/>
+    </row>
     <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7071" s="2"/>
       <c r="K7071" s="1"/>
     </row>
     <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7072" s="2"/>
       <c r="K7072" s="1"/>
     </row>
     <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7073" s="1"/>
     </row>
     <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7074" s="2"/>
       <c r="K7074" s="1"/>
     </row>
     <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
@@ -40878,6 +41418,7 @@
       <c r="K7075" s="1"/>
     </row>
     <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7076" s="2"/>
       <c r="K7076" s="1"/>
     </row>
     <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
@@ -40888,6 +41429,7 @@
       <c r="K7078" s="1"/>
     </row>
     <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7079" s="2"/>
       <c r="K7079" s="1"/>
     </row>
     <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
@@ -40914,15 +41456,19 @@
       <c r="K7085" s="1"/>
     </row>
     <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7086" s="2"/>
       <c r="K7086" s="1"/>
     </row>
     <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7087" s="2"/>
       <c r="K7087" s="1"/>
     </row>
     <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7088" s="2"/>
       <c r="K7088" s="1"/>
     </row>
     <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7089" s="2"/>
       <c r="K7089" s="1"/>
     </row>
     <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
@@ -40944,6 +41490,7 @@
       <c r="K7094" s="1"/>
     </row>
     <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7095" s="2"/>
       <c r="K7095" s="1"/>
     </row>
     <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
@@ -40951,9 +41498,11 @@
       <c r="K7096" s="1"/>
     </row>
     <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7097" s="2"/>
       <c r="K7097" s="1"/>
     </row>
     <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7098" s="2"/>
       <c r="K7098" s="1"/>
     </row>
     <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
@@ -40961,6 +41510,7 @@
       <c r="K7099" s="1"/>
     </row>
     <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7100" s="2"/>
       <c r="K7100" s="1"/>
     </row>
     <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
@@ -40972,6 +41522,7 @@
       <c r="K7102" s="1"/>
     </row>
     <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7103" s="2"/>
       <c r="K7103" s="1"/>
     </row>
     <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
@@ -40986,6 +41537,10 @@
       <c r="J7106" s="2"/>
       <c r="K7106" s="1"/>
     </row>
+    <row r="7107" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7107" s="2"/>
+      <c r="K7107" s="1"/>
+    </row>
     <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7108" s="2"/>
       <c r="K7108" s="1"/>
@@ -40995,6 +41550,7 @@
       <c r="K7109" s="1"/>
     </row>
     <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7110" s="2"/>
       <c r="K7110" s="1"/>
     </row>
     <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
@@ -41006,6 +41562,7 @@
       <c r="K7112" s="1"/>
     </row>
     <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7113" s="2"/>
       <c r="K7113" s="1"/>
     </row>
     <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
@@ -41016,10 +41573,15 @@
       <c r="J7115" s="2"/>
       <c r="K7115" s="1"/>
     </row>
+    <row r="7116" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7116" s="1"/>
+    </row>
     <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7117" s="2"/>
       <c r="K7117" s="1"/>
     </row>
     <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7118" s="2"/>
       <c r="K7118" s="1"/>
     </row>
     <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
@@ -41027,6 +41589,7 @@
       <c r="K7119" s="1"/>
     </row>
     <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7120" s="2"/>
       <c r="K7120" s="1"/>
     </row>
     <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
@@ -41041,6 +41604,7 @@
       <c r="K7123" s="1"/>
     </row>
     <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7124" s="2"/>
       <c r="K7124" s="1"/>
     </row>
     <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
@@ -41063,6 +41627,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7130" s="2"/>
       <c r="K7130" s="1"/>
     </row>
     <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
@@ -41082,25 +41647,37 @@
       <c r="K7134" s="1"/>
     </row>
     <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7135" s="2"/>
       <c r="K7135" s="1"/>
     </row>
     <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7136" s="2"/>
       <c r="K7136" s="1"/>
     </row>
     <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7137" s="2"/>
       <c r="K7137" s="1"/>
     </row>
     <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7138" s="2"/>
       <c r="K7138" s="1"/>
     </row>
+    <row r="7139" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7139" s="2"/>
+      <c r="K7139" s="1"/>
+    </row>
     <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7140" s="2"/>
       <c r="K7140" s="1"/>
     </row>
     <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7141" s="2"/>
       <c r="K7141" s="1"/>
     </row>
+    <row r="7142" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7142" s="2"/>
+      <c r="K7142" s="1"/>
+    </row>
     <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7143" s="1"/>
     </row>
@@ -41108,6 +41685,7 @@
       <c r="K7144" s="1"/>
     </row>
     <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7145" s="2"/>
       <c r="K7145" s="1"/>
     </row>
     <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
@@ -41115,15 +41693,22 @@
       <c r="K7146" s="1"/>
     </row>
     <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7147" s="2"/>
       <c r="K7147" s="1"/>
     </row>
     <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7148" s="1"/>
     </row>
+    <row r="7149" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7149" s="2"/>
+      <c r="K7149" s="1"/>
+    </row>
     <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7150" s="2"/>
       <c r="K7150" s="1"/>
     </row>
     <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7151" s="2"/>
       <c r="K7151" s="1"/>
     </row>
     <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
@@ -41137,6 +41722,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7155" s="2"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
@@ -41155,9 +41741,11 @@
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7160" s="2"/>
       <c r="K7160" s="1"/>
     </row>
     <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7161" s="2"/>
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
@@ -41165,9 +41753,11 @@
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7163" s="2"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7164" s="2"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
@@ -41175,6 +41765,7 @@
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7166" s="2"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
@@ -41191,10 +41782,14 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7171" s="2"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7172" s="1"/>
+    </row>
+    <row r="7173" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7173" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Indigo-Construction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AFCEE315-48CC-4C2A-8CA3-9525C6B85507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{68284CC6-663F-4BEB-B9CA-6A8568713EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="41">
   <si>
     <t>Company Name</t>
   </si>
@@ -108,6 +108,9 @@
   </si>
   <si>
     <t>Speed Mangement-C</t>
+  </si>
+  <si>
+    <t>Dangers of Distracted Driving</t>
   </si>
   <si>
     <t>Camera Event Management Orientation for Drivers</t>
@@ -532,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="B1:K7400"/>
+  <dimension ref="A1:K7404"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -547,47 +550,47 @@
     <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2">
         <v>5162</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F2" t="s">
         <v>19</v>
@@ -608,7 +611,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H3" s="2"/>
       <c r="I3" s="1"/>
       <c r="J3" s="2"/>
@@ -616,15 +619,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4">
         <v>5166</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4" t="s">
         <v>19</v>
@@ -645,15 +648,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5">
         <v>5168</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5" t="s">
         <v>19</v>
@@ -674,15 +677,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6">
         <v>5163</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F6" t="s">
         <v>19</v>
@@ -703,15 +706,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7">
         <v>5159</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s">
         <v>19</v>
@@ -732,15 +735,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8">
         <v>5165</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
         <v>19</v>
@@ -761,15 +764,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9">
         <v>5160</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s">
         <v>19</v>
@@ -790,15 +793,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10">
         <v>5161</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F10" t="s">
         <v>19</v>
@@ -819,15 +822,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11">
         <v>5167</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F11" t="s">
         <v>19</v>
@@ -848,15 +851,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12">
         <v>5164</v>
       </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F12" t="s">
         <v>19</v>
@@ -877,18 +880,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C13">
         <v>5162</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
@@ -906,18 +909,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C14">
         <v>5166</v>
       </c>
       <c r="D14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G14" t="s">
         <v>12</v>
@@ -935,7 +938,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H15" s="2"/>
       <c r="I15" s="1"/>
       <c r="J15" s="2"/>
@@ -943,18 +946,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C16">
         <v>5168</v>
       </c>
       <c r="D16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
@@ -974,16 +977,16 @@
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C17">
         <v>5163</v>
       </c>
       <c r="D17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G17" t="s">
         <v>13</v>
@@ -1003,16 +1006,16 @@
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C18">
         <v>5159</v>
       </c>
       <c r="D18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G18" t="s">
         <v>13</v>
@@ -1032,16 +1035,16 @@
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19">
         <v>5165</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
@@ -1061,16 +1064,16 @@
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C20">
         <v>5160</v>
       </c>
       <c r="D20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G20" t="s">
         <v>12</v>
@@ -1098,16 +1101,16 @@
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C22">
         <v>5161</v>
       </c>
       <c r="D22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G22" t="s">
         <v>13</v>
@@ -1127,16 +1130,16 @@
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C23">
         <v>5167</v>
       </c>
       <c r="D23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G23" t="s">
         <v>13</v>
@@ -1156,16 +1159,16 @@
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C24">
         <v>5164</v>
       </c>
       <c r="D24" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G24" t="s">
         <v>12</v>
@@ -1193,13 +1196,13 @@
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C26">
         <v>5162</v>
       </c>
       <c r="D26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F26" t="s">
         <v>20</v>
@@ -1222,13 +1225,13 @@
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C27">
         <v>5166</v>
       </c>
       <c r="D27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F27" t="s">
         <v>20</v>
@@ -1251,13 +1254,13 @@
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C28">
         <v>5168</v>
       </c>
       <c r="D28" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F28" t="s">
         <v>20</v>
@@ -1280,13 +1283,13 @@
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C29">
         <v>5163</v>
       </c>
       <c r="D29" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F29" t="s">
         <v>20</v>
@@ -1309,13 +1312,13 @@
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C30">
         <v>5159</v>
       </c>
       <c r="D30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F30" t="s">
         <v>20</v>
@@ -1338,13 +1341,13 @@
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C31">
         <v>5165</v>
       </c>
       <c r="D31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F31" t="s">
         <v>20</v>
@@ -1367,13 +1370,13 @@
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C32">
         <v>5160</v>
       </c>
       <c r="D32" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F32" t="s">
         <v>20</v>
@@ -1404,13 +1407,13 @@
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C34">
         <v>5161</v>
       </c>
       <c r="D34" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F34" t="s">
         <v>20</v>
@@ -1433,13 +1436,13 @@
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C35">
         <v>5167</v>
       </c>
       <c r="D35" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F35" t="s">
         <v>20</v>
@@ -1462,13 +1465,13 @@
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C36">
         <v>5164</v>
       </c>
       <c r="D36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F36" t="s">
         <v>20</v>
@@ -1491,13 +1494,13 @@
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C37">
         <v>5162</v>
       </c>
       <c r="D37" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F37" t="s">
         <v>21</v>
@@ -1520,13 +1523,13 @@
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C38">
         <v>5166</v>
       </c>
       <c r="D38" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F38" t="s">
         <v>21</v>
@@ -1549,13 +1552,13 @@
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C39">
         <v>5168</v>
       </c>
       <c r="D39" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F39" t="s">
         <v>21</v>
@@ -1578,13 +1581,13 @@
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C40">
         <v>5163</v>
       </c>
       <c r="D40" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F40" t="s">
         <v>21</v>
@@ -1607,13 +1610,13 @@
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C41">
         <v>5159</v>
       </c>
       <c r="D41" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F41" t="s">
         <v>21</v>
@@ -1636,13 +1639,13 @@
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C42">
         <v>5165</v>
       </c>
       <c r="D42" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F42" t="s">
         <v>21</v>
@@ -1665,13 +1668,13 @@
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C43">
         <v>5160</v>
       </c>
       <c r="D43" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F43" t="s">
         <v>21</v>
@@ -1694,13 +1697,13 @@
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C44">
         <v>5161</v>
       </c>
       <c r="D44" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F44" t="s">
         <v>21</v>
@@ -1723,13 +1726,13 @@
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C45">
         <v>5167</v>
       </c>
       <c r="D45" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F45" t="s">
         <v>21</v>
@@ -1752,13 +1755,13 @@
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C46">
         <v>5164</v>
       </c>
       <c r="D46" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F46" t="s">
         <v>21</v>
@@ -1789,13 +1792,13 @@
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C48">
         <v>5162</v>
       </c>
       <c r="D48" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F48" t="s">
         <v>16</v>
@@ -1818,13 +1821,13 @@
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C49">
         <v>5166</v>
       </c>
       <c r="D49" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F49" t="s">
         <v>16</v>
@@ -1855,13 +1858,13 @@
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C51">
         <v>5168</v>
       </c>
       <c r="D51" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F51" t="s">
         <v>16</v>
@@ -1884,13 +1887,13 @@
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C52">
         <v>5163</v>
       </c>
       <c r="D52" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F52" t="s">
         <v>16</v>
@@ -1913,13 +1916,13 @@
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C53">
         <v>5159</v>
       </c>
       <c r="D53" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F53" t="s">
         <v>16</v>
@@ -1942,13 +1945,13 @@
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C54">
         <v>5165</v>
       </c>
       <c r="D54" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F54" t="s">
         <v>16</v>
@@ -1971,13 +1974,13 @@
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C55">
         <v>5160</v>
       </c>
       <c r="D55" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F55" t="s">
         <v>16</v>
@@ -2000,13 +2003,13 @@
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C56">
         <v>5161</v>
       </c>
       <c r="D56" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F56" t="s">
         <v>16</v>
@@ -2029,13 +2032,13 @@
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C57">
         <v>5167</v>
       </c>
       <c r="D57" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F57" t="s">
         <v>16</v>
@@ -2066,13 +2069,13 @@
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C59">
         <v>5164</v>
       </c>
       <c r="D59" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F59" t="s">
         <v>16</v>
@@ -2095,13 +2098,13 @@
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C60">
         <v>5668</v>
       </c>
       <c r="D60" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F60" t="s">
         <v>18</v>
@@ -2124,13 +2127,13 @@
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C61">
         <v>5167</v>
       </c>
       <c r="D61" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F61" t="s">
         <v>18</v>
@@ -2153,13 +2156,13 @@
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C62">
         <v>5168</v>
       </c>
       <c r="D62" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F62" t="s">
         <v>22</v>
@@ -2182,13 +2185,13 @@
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C63">
         <v>5162</v>
       </c>
       <c r="D63" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F63" t="s">
         <v>22</v>
@@ -2211,13 +2214,13 @@
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C64">
         <v>5166</v>
       </c>
       <c r="D64" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F64" t="s">
         <v>22</v>
@@ -2248,13 +2251,13 @@
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C66">
         <v>5163</v>
       </c>
       <c r="D66" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F66" t="s">
         <v>22</v>
@@ -2277,13 +2280,13 @@
     </row>
     <row r="67" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C67">
         <v>5159</v>
       </c>
       <c r="D67" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F67" t="s">
         <v>22</v>
@@ -2306,13 +2309,13 @@
     </row>
     <row r="68" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C68">
         <v>5165</v>
       </c>
       <c r="D68" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F68" t="s">
         <v>22</v>
@@ -2335,13 +2338,13 @@
     </row>
     <row r="69" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C69">
         <v>5160</v>
       </c>
       <c r="D69" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F69" t="s">
         <v>22</v>
@@ -2364,13 +2367,13 @@
     </row>
     <row r="70" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C70">
         <v>5161</v>
       </c>
       <c r="D70" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F70" t="s">
         <v>22</v>
@@ -2393,13 +2396,13 @@
     </row>
     <row r="71" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C71">
         <v>5164</v>
       </c>
       <c r="D71" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F71" t="s">
         <v>22</v>
@@ -2430,16 +2433,16 @@
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C73">
         <v>5668</v>
       </c>
       <c r="D73" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F73" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G73" t="s">
         <v>10</v>
@@ -2459,13 +2462,13 @@
     </row>
     <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C74">
         <v>5162</v>
       </c>
       <c r="D74" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F74" t="s">
         <v>17</v>
@@ -2488,13 +2491,13 @@
     </row>
     <row r="75" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C75">
         <v>5166</v>
       </c>
       <c r="D75" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F75" t="s">
         <v>17</v>
@@ -2517,13 +2520,13 @@
     </row>
     <row r="76" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C76">
         <v>5168</v>
       </c>
       <c r="D76" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F76" t="s">
         <v>17</v>
@@ -2546,13 +2549,13 @@
     </row>
     <row r="77" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C77">
         <v>5938</v>
       </c>
       <c r="D77" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F77" t="s">
         <v>17</v>
@@ -2575,13 +2578,13 @@
     </row>
     <row r="78" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C78">
         <v>5668</v>
       </c>
       <c r="D78" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F78" t="s">
         <v>17</v>
@@ -2604,13 +2607,13 @@
     </row>
     <row r="79" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C79">
         <v>5163</v>
       </c>
       <c r="D79" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F79" t="s">
         <v>17</v>
@@ -2633,13 +2636,13 @@
     </row>
     <row r="80" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C80">
         <v>5159</v>
       </c>
       <c r="D80" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F80" t="s">
         <v>17</v>
@@ -2662,13 +2665,13 @@
     </row>
     <row r="81" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C81">
         <v>5165</v>
       </c>
       <c r="D81" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F81" t="s">
         <v>17</v>
@@ -2699,13 +2702,13 @@
     </row>
     <row r="83" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C83">
         <v>5160</v>
       </c>
       <c r="D83" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F83" t="s">
         <v>17</v>
@@ -2728,22 +2731,22 @@
     </row>
     <row r="84" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C84">
         <v>5167</v>
       </c>
       <c r="D84" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F84" t="s">
         <v>17</v>
       </c>
       <c r="G84" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H84" s="2">
-        <v>2.3148148148148147E-5</v>
+        <v>1.6944444444444446E-2</v>
       </c>
       <c r="I84" s="1">
         <v>46219.673032407409</v>
@@ -2756,241 +2759,542 @@
       </c>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H85" s="2"/>
-      <c r="I85" s="1"/>
-      <c r="J85" s="2"/>
+      <c r="B85" t="s">
+        <v>26</v>
+      </c>
+      <c r="C85">
+        <v>5164</v>
+      </c>
+      <c r="D85" t="s">
+        <v>36</v>
+      </c>
+      <c r="F85" t="s">
+        <v>17</v>
+      </c>
+      <c r="G85" t="s">
+        <v>10</v>
+      </c>
+      <c r="H85" s="2">
+        <v>8.1712962962962963E-3</v>
+      </c>
+      <c r="I85" s="1">
+        <v>46219.673032407409</v>
+      </c>
+      <c r="J85" s="2">
+        <v>0</v>
+      </c>
       <c r="K85" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="86" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C86">
-        <v>5164</v>
+        <v>5937</v>
       </c>
       <c r="D86" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F86" t="s">
         <v>17</v>
       </c>
       <c r="G86" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H86" s="2">
-        <v>8.1712962962962963E-3</v>
+        <v>0</v>
       </c>
       <c r="I86" s="1">
-        <v>46219.673032407409</v>
+        <v>46219.673726851855</v>
       </c>
       <c r="J86" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K86" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="87" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B87" t="s">
-        <v>25</v>
-      </c>
-      <c r="C87">
-        <v>5937</v>
-      </c>
-      <c r="D87" t="s">
-        <v>38</v>
-      </c>
-      <c r="F87" t="s">
+      <c r="H87" s="2"/>
+      <c r="I87" s="1"/>
+      <c r="J87" s="2"/>
+      <c r="K87" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="88" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B88" t="s">
+        <v>26</v>
+      </c>
+      <c r="C88">
+        <v>5936</v>
+      </c>
+      <c r="D88" t="s">
+        <v>40</v>
+      </c>
+      <c r="F88" t="s">
         <v>17</v>
       </c>
-      <c r="G87" t="s">
-        <v>12</v>
-      </c>
-      <c r="H87" s="2">
-        <v>0</v>
-      </c>
-      <c r="I87" s="1">
-        <v>46219.673726851855</v>
-      </c>
-      <c r="J87" s="2">
-        <v>2</v>
-      </c>
-      <c r="K87" s="1" t="s">
+      <c r="G88" t="s">
+        <v>10</v>
+      </c>
+      <c r="H88" s="2">
+        <v>8.2523148148148148E-3</v>
+      </c>
+      <c r="I88" s="1">
+        <v>46219.674421296295</v>
+      </c>
+      <c r="J88" s="2">
+        <v>1</v>
+      </c>
+      <c r="K88" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="88" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H88" s="2"/>
-      <c r="I88" s="1"/>
-      <c r="J88" s="2"/>
-      <c r="K88" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C89">
-        <v>5936</v>
+        <v>5162</v>
       </c>
       <c r="D89" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F89" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G89" t="s">
         <v>10</v>
       </c>
       <c r="H89" s="2">
-        <v>8.2523148148148148E-3</v>
+        <v>7.1759259259259259E-3</v>
       </c>
       <c r="I89" s="1">
-        <v>46219.674421296295</v>
+        <v>46237.809027777781</v>
       </c>
       <c r="J89" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K89" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H90" s="2"/>
-      <c r="I90" s="1"/>
-      <c r="J90" s="2"/>
-      <c r="K90" s="1"/>
+      <c r="B90" t="s">
+        <v>26</v>
+      </c>
+      <c r="C90">
+        <v>5166</v>
+      </c>
+      <c r="D90" t="s">
+        <v>28</v>
+      </c>
+      <c r="F90" t="s">
+        <v>23</v>
+      </c>
+      <c r="G90" t="s">
+        <v>13</v>
+      </c>
+      <c r="H90" s="2">
+        <v>0</v>
+      </c>
+      <c r="I90" s="1">
+        <v>46237.809027777781</v>
+      </c>
+      <c r="J90" s="2">
+        <v>0</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="91" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H91" s="2"/>
-      <c r="I91" s="1"/>
-      <c r="J91" s="2"/>
-      <c r="K91" s="1"/>
+      <c r="B91" t="s">
+        <v>26</v>
+      </c>
+      <c r="C91">
+        <v>5168</v>
+      </c>
+      <c r="D91" t="s">
+        <v>29</v>
+      </c>
+      <c r="F91" t="s">
+        <v>23</v>
+      </c>
+      <c r="G91" t="s">
+        <v>12</v>
+      </c>
+      <c r="H91" s="2">
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="I91" s="1">
+        <v>46237.80972222222</v>
+      </c>
+      <c r="J91" s="2">
+        <v>0</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H92" s="2"/>
       <c r="I92" s="1"/>
       <c r="J92" s="2"/>
-      <c r="K92" s="1"/>
+      <c r="K92" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H93" s="2"/>
-      <c r="I93" s="1"/>
-      <c r="J93" s="2"/>
-      <c r="K93" s="1"/>
+      <c r="B93" t="s">
+        <v>26</v>
+      </c>
+      <c r="C93">
+        <v>5938</v>
+      </c>
+      <c r="D93" t="s">
+        <v>38</v>
+      </c>
+      <c r="F93" t="s">
+        <v>23</v>
+      </c>
+      <c r="G93" t="s">
+        <v>12</v>
+      </c>
+      <c r="H93" s="2">
+        <v>3.4722222222222222E-5</v>
+      </c>
+      <c r="I93" s="1">
+        <v>46237.810416666667</v>
+      </c>
+      <c r="J93" s="2">
+        <v>0</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H94" s="2"/>
       <c r="I94" s="1"/>
       <c r="J94" s="2"/>
-      <c r="K94" s="1"/>
+      <c r="K94" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H95" s="2"/>
-      <c r="I95" s="1"/>
-      <c r="J95" s="2"/>
-      <c r="K95" s="1"/>
+      <c r="B95" t="s">
+        <v>26</v>
+      </c>
+      <c r="C95">
+        <v>5668</v>
+      </c>
+      <c r="D95" t="s">
+        <v>37</v>
+      </c>
+      <c r="F95" t="s">
+        <v>23</v>
+      </c>
+      <c r="G95" t="s">
+        <v>13</v>
+      </c>
+      <c r="H95" s="2">
+        <v>0</v>
+      </c>
+      <c r="I95" s="1">
+        <v>46237.810416666667</v>
+      </c>
+      <c r="J95" s="2">
+        <v>0</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="96" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H96" s="2"/>
-      <c r="I96" s="1"/>
-      <c r="J96" s="2"/>
-      <c r="K96" s="1"/>
-    </row>
-    <row r="97" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H97" s="2"/>
-      <c r="I97" s="1"/>
-      <c r="J97" s="2"/>
-      <c r="K97" s="1"/>
-    </row>
-    <row r="98" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H98" s="2"/>
-      <c r="I98" s="1"/>
-      <c r="J98" s="2"/>
-      <c r="K98" s="1"/>
-    </row>
-    <row r="99" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H99" s="2"/>
-      <c r="I99" s="1"/>
-      <c r="J99" s="2"/>
-      <c r="K99" s="1"/>
-    </row>
-    <row r="100" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H100" s="2"/>
-      <c r="I100" s="1"/>
-      <c r="J100" s="2"/>
-      <c r="K100" s="1"/>
-    </row>
-    <row r="101" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H101" s="2"/>
-      <c r="I101" s="1"/>
-      <c r="J101" s="2"/>
-      <c r="K101" s="1"/>
-    </row>
-    <row r="102" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H102" s="2"/>
-      <c r="I102" s="1"/>
-      <c r="J102" s="2"/>
-      <c r="K102" s="1"/>
-    </row>
-    <row r="103" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H103" s="2"/>
-      <c r="I103" s="1"/>
-      <c r="J103" s="2"/>
-      <c r="K103" s="1"/>
-    </row>
-    <row r="104" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="B96" t="s">
+        <v>26</v>
+      </c>
+      <c r="C96">
+        <v>5163</v>
+      </c>
+      <c r="D96" t="s">
+        <v>30</v>
+      </c>
+      <c r="F96" t="s">
+        <v>23</v>
+      </c>
+      <c r="G96" t="s">
+        <v>13</v>
+      </c>
+      <c r="H96" s="2">
+        <v>0</v>
+      </c>
+      <c r="I96" s="1">
+        <v>46237.811111111114</v>
+      </c>
+      <c r="J96" s="2">
+        <v>0</v>
+      </c>
+      <c r="K96" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="97" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B97" t="s">
+        <v>26</v>
+      </c>
+      <c r="C97">
+        <v>5159</v>
+      </c>
+      <c r="D97" t="s">
+        <v>31</v>
+      </c>
+      <c r="F97" t="s">
+        <v>23</v>
+      </c>
+      <c r="G97" t="s">
+        <v>10</v>
+      </c>
+      <c r="H97" s="2">
+        <v>7.9282407407407409E-3</v>
+      </c>
+      <c r="I97" s="1">
+        <v>46237.811805555553</v>
+      </c>
+      <c r="J97" s="2">
+        <v>0</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="98" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B98" t="s">
+        <v>26</v>
+      </c>
+      <c r="C98">
+        <v>5165</v>
+      </c>
+      <c r="D98" t="s">
+        <v>32</v>
+      </c>
+      <c r="F98" t="s">
+        <v>23</v>
+      </c>
+      <c r="G98" t="s">
+        <v>13</v>
+      </c>
+      <c r="H98" s="2">
+        <v>0</v>
+      </c>
+      <c r="I98" s="1">
+        <v>46237.8125</v>
+      </c>
+      <c r="J98" s="2">
+        <v>0</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="99" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B99" t="s">
+        <v>26</v>
+      </c>
+      <c r="C99">
+        <v>5160</v>
+      </c>
+      <c r="D99" t="s">
+        <v>33</v>
+      </c>
+      <c r="F99" t="s">
+        <v>23</v>
+      </c>
+      <c r="G99" t="s">
+        <v>10</v>
+      </c>
+      <c r="H99" s="2">
+        <v>7.3148148148148148E-3</v>
+      </c>
+      <c r="I99" s="1">
+        <v>46237.8125</v>
+      </c>
+      <c r="J99" s="2">
+        <v>0</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="100" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B100" t="s">
+        <v>26</v>
+      </c>
+      <c r="C100">
+        <v>5167</v>
+      </c>
+      <c r="D100" t="s">
+        <v>35</v>
+      </c>
+      <c r="F100" t="s">
+        <v>23</v>
+      </c>
+      <c r="G100" t="s">
+        <v>10</v>
+      </c>
+      <c r="H100" s="2">
+        <v>7.858796296296296E-3</v>
+      </c>
+      <c r="I100" s="1">
+        <v>46237.813194444447</v>
+      </c>
+      <c r="J100" s="2">
+        <v>0</v>
+      </c>
+      <c r="K100" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="101" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B101" t="s">
+        <v>26</v>
+      </c>
+      <c r="C101">
+        <v>5164</v>
+      </c>
+      <c r="D101" t="s">
+        <v>36</v>
+      </c>
+      <c r="F101" t="s">
+        <v>23</v>
+      </c>
+      <c r="G101" t="s">
+        <v>10</v>
+      </c>
+      <c r="H101" s="2">
+        <v>7.4074074074074077E-3</v>
+      </c>
+      <c r="I101" s="1">
+        <v>46237.813888888886</v>
+      </c>
+      <c r="J101" s="2">
+        <v>0</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="102" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B102" t="s">
+        <v>26</v>
+      </c>
+      <c r="C102">
+        <v>5937</v>
+      </c>
+      <c r="D102" t="s">
+        <v>39</v>
+      </c>
+      <c r="F102" t="s">
+        <v>23</v>
+      </c>
+      <c r="G102" t="s">
+        <v>13</v>
+      </c>
+      <c r="H102" s="2">
+        <v>0</v>
+      </c>
+      <c r="I102" s="1">
+        <v>46237.813888888886</v>
+      </c>
+      <c r="J102" s="2">
+        <v>0</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="103" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B103" t="s">
+        <v>26</v>
+      </c>
+      <c r="C103">
+        <v>5936</v>
+      </c>
+      <c r="D103" t="s">
+        <v>40</v>
+      </c>
+      <c r="F103" t="s">
+        <v>23</v>
+      </c>
+      <c r="G103" t="s">
+        <v>10</v>
+      </c>
+      <c r="H103" s="2">
+        <v>8.0439814814814818E-3</v>
+      </c>
+      <c r="I103" s="1">
+        <v>46237.814583333333</v>
+      </c>
+      <c r="J103" s="2">
+        <v>0</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="104" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H104" s="2"/>
       <c r="I104" s="1"/>
       <c r="J104" s="2"/>
       <c r="K104" s="1"/>
     </row>
-    <row r="105" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H105" s="2"/>
       <c r="I105" s="1"/>
       <c r="J105" s="2"/>
       <c r="K105" s="1"/>
     </row>
-    <row r="106" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H106" s="2"/>
       <c r="I106" s="1"/>
       <c r="J106" s="2"/>
       <c r="K106" s="1"/>
     </row>
-    <row r="107" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H107" s="2"/>
       <c r="I107" s="1"/>
       <c r="J107" s="2"/>
       <c r="K107" s="1"/>
     </row>
-    <row r="108" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H108" s="2"/>
       <c r="I108" s="1"/>
       <c r="J108" s="2"/>
       <c r="K108" s="1"/>
     </row>
-    <row r="109" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H109" s="2"/>
       <c r="I109" s="1"/>
       <c r="J109" s="2"/>
       <c r="K109" s="1"/>
     </row>
-    <row r="110" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H110" s="2"/>
       <c r="I110" s="1"/>
       <c r="J110" s="2"/>
       <c r="K110" s="1"/>
     </row>
-    <row r="111" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H111" s="2"/>
       <c r="I111" s="1"/>
       <c r="J111" s="2"/>
       <c r="K111" s="1"/>
     </row>
-    <row r="112" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H112" s="2"/>
       <c r="I112" s="1"/>
       <c r="J112" s="2"/>
@@ -44452,6 +44756,7 @@
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
@@ -44466,11 +44771,13 @@
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -44481,10 +44788,13 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7162" s="2"/>
+      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
@@ -44502,14 +44812,17 @@
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -44520,14 +44833,17 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
@@ -44554,6 +44870,7 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
@@ -44562,6 +44879,7 @@
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
@@ -44574,22 +44892,27 @@
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -44608,6 +44931,7 @@
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -44618,10 +44942,12 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
@@ -44630,10 +44956,12 @@
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
@@ -44647,82 +44975,97 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7201" s="2"/>
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7202" s="2"/>
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7203" s="2"/>
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7204" s="2"/>
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7205" s="2"/>
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7207" s="2"/>
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7209" s="2"/>
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7211" s="2"/>
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7212" s="2"/>
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7216" s="2"/>
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
@@ -44736,6 +45079,7 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -44746,6 +45090,7 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
@@ -44753,6 +45098,7 @@
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
@@ -44761,86 +45107,99 @@
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7233" s="2"/>
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7235" s="2"/>
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7238" s="2"/>
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7239" s="2"/>
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7243" s="2"/>
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7244" s="2"/>
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7245" s="2"/>
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7248" s="2"/>
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -44857,26 +45216,32 @@
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
@@ -44907,6 +45272,7 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
@@ -44916,10 +45282,12 @@
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
@@ -44932,14 +45300,17 @@
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
@@ -44948,14 +45319,17 @@
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
@@ -44974,26 +45348,32 @@
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -45012,6 +45392,7 @@
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
@@ -45020,10 +45401,12 @@
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
@@ -45032,6 +45415,7 @@
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
@@ -45044,10 +45428,12 @@
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
@@ -45056,6 +45442,7 @@
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
@@ -45064,14 +45451,17 @@
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
@@ -45080,14 +45470,17 @@
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
@@ -45104,76 +45497,85 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7314" s="2"/>
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7317" s="2"/>
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7318" s="2"/>
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7323" s="2"/>
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7324" s="2"/>
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7325" s="2"/>
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7328" s="2"/>
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
@@ -45187,31 +45589,38 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
@@ -45224,10 +45633,12 @@
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
@@ -45236,10 +45647,12 @@
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
@@ -45248,6 +45661,7 @@
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -45262,10 +45676,12 @@
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
@@ -45274,10 +45690,12 @@
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
@@ -45291,6 +45709,7 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -45306,14 +45725,17 @@
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -45331,14 +45753,17 @@
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
@@ -45351,10 +45776,12 @@
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
@@ -45363,14 +45790,17 @@
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
@@ -45379,10 +45809,12 @@
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
@@ -45391,14 +45823,17 @@
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
@@ -45420,6 +45855,7 @@
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
@@ -45428,39 +45864,65 @@
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7393" s="2"/>
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7394" s="1"/>
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7395" s="2"/>
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7396" s="2"/>
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7397" s="2"/>
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7399" s="2"/>
+      <c r="I7399" s="1"/>
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
+    </row>
+    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7401" s="2"/>
+      <c r="I7401" s="1"/>
+    </row>
+    <row r="7402" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7402" s="2"/>
+      <c r="I7402" s="1"/>
+    </row>
+    <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7403" s="1"/>
+    </row>
+    <row r="7404" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7404" s="2"/>
+      <c r="I7404" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Indigo-Construction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{68284CC6-663F-4BEB-B9CA-6A8568713EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E83318DA-70A4-4519-BD6C-903BE05D1760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="41">
   <si>
     <t>Company Name</t>
   </si>
@@ -535,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7404"/>
+  <dimension ref="A1:K7403"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -611,7 +611,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H3" s="2"/>
       <c r="I3" s="1"/>
       <c r="J3" s="2"/>
@@ -764,7 +764,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>26</v>
       </c>
@@ -880,7 +880,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>26</v>
       </c>
@@ -1194,7 +1194,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>26</v>
       </c>
@@ -1368,7 +1368,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>26</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>26</v>
       </c>
@@ -1943,7 +1943,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>26</v>
       </c>
@@ -2460,7 +2460,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>26</v>
       </c>
@@ -2692,7 +2692,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H82" s="2"/>
       <c r="I82" s="1"/>
       <c r="J82" s="2"/>
@@ -2905,7 +2905,7 @@
         <v>46237.809027777781</v>
       </c>
       <c r="J90" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K90" s="1" t="s">
         <v>11</v>
@@ -2925,64 +2925,85 @@
         <v>23</v>
       </c>
       <c r="G91" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H91" s="2">
-        <v>3.3333333333333335E-3</v>
+        <v>1.1898148148148149E-2</v>
       </c>
       <c r="I91" s="1">
         <v>46237.80972222222</v>
       </c>
       <c r="J91" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K91" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H92" s="2"/>
-      <c r="I92" s="1"/>
-      <c r="J92" s="2"/>
+    <row r="92" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B92" t="s">
+        <v>26</v>
+      </c>
+      <c r="C92">
+        <v>5938</v>
+      </c>
+      <c r="D92" t="s">
+        <v>38</v>
+      </c>
+      <c r="F92" t="s">
+        <v>23</v>
+      </c>
+      <c r="G92" t="s">
+        <v>12</v>
+      </c>
+      <c r="H92" s="2">
+        <v>3.4722222222222222E-5</v>
+      </c>
+      <c r="I92" s="1">
+        <v>46237.810416666667</v>
+      </c>
+      <c r="J92" s="2">
+        <v>3</v>
+      </c>
       <c r="K92" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="93" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H93" s="2"/>
+      <c r="I93" s="1"/>
+      <c r="J93" s="2"/>
+      <c r="K93" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="93" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B93" t="s">
+    <row r="94" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B94" t="s">
         <v>26</v>
       </c>
-      <c r="C93">
-        <v>5938</v>
-      </c>
-      <c r="D93" t="s">
-        <v>38</v>
-      </c>
-      <c r="F93" t="s">
+      <c r="C94">
+        <v>5668</v>
+      </c>
+      <c r="D94" t="s">
+        <v>37</v>
+      </c>
+      <c r="F94" t="s">
         <v>23</v>
       </c>
-      <c r="G93" t="s">
-        <v>12</v>
-      </c>
-      <c r="H93" s="2">
-        <v>3.4722222222222222E-5</v>
-      </c>
-      <c r="I93" s="1">
+      <c r="G94" t="s">
+        <v>10</v>
+      </c>
+      <c r="H94" s="2">
+        <v>1.0046296296296296E-2</v>
+      </c>
+      <c r="I94" s="1">
         <v>46237.810416666667</v>
       </c>
-      <c r="J93" s="2">
-        <v>0</v>
-      </c>
-      <c r="K93" s="1" t="s">
+      <c r="J94" s="2">
+        <v>1</v>
+      </c>
+      <c r="K94" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="94" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H94" s="2"/>
-      <c r="I94" s="1"/>
-      <c r="J94" s="2"/>
-      <c r="K94" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.25">
@@ -2990,10 +3011,10 @@
         <v>26</v>
       </c>
       <c r="C95">
-        <v>5668</v>
+        <v>5163</v>
       </c>
       <c r="D95" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F95" t="s">
         <v>23</v>
@@ -3005,10 +3026,10 @@
         <v>0</v>
       </c>
       <c r="I95" s="1">
-        <v>46237.810416666667</v>
+        <v>46237.811111111114</v>
       </c>
       <c r="J95" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K95" s="1" t="s">
         <v>11</v>
@@ -3019,22 +3040,22 @@
         <v>26</v>
       </c>
       <c r="C96">
-        <v>5163</v>
+        <v>5159</v>
       </c>
       <c r="D96" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F96" t="s">
         <v>23</v>
       </c>
       <c r="G96" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H96" s="2">
-        <v>0</v>
+        <v>7.9282407407407409E-3</v>
       </c>
       <c r="I96" s="1">
-        <v>46237.811111111114</v>
+        <v>46237.811805555553</v>
       </c>
       <c r="J96" s="2">
         <v>0</v>
@@ -3048,25 +3069,25 @@
         <v>26</v>
       </c>
       <c r="C97">
-        <v>5159</v>
+        <v>5165</v>
       </c>
       <c r="D97" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F97" t="s">
         <v>23</v>
       </c>
       <c r="G97" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H97" s="2">
-        <v>7.9282407407407409E-3</v>
+        <v>0</v>
       </c>
       <c r="I97" s="1">
-        <v>46237.811805555553</v>
+        <v>46237.8125</v>
       </c>
       <c r="J97" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K97" s="1" t="s">
         <v>11</v>
@@ -3077,19 +3098,19 @@
         <v>26</v>
       </c>
       <c r="C98">
-        <v>5165</v>
+        <v>5160</v>
       </c>
       <c r="D98" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F98" t="s">
         <v>23</v>
       </c>
       <c r="G98" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H98" s="2">
-        <v>0</v>
+        <v>7.3148148148148148E-3</v>
       </c>
       <c r="I98" s="1">
         <v>46237.8125</v>
@@ -3106,10 +3127,10 @@
         <v>26</v>
       </c>
       <c r="C99">
-        <v>5160</v>
+        <v>5167</v>
       </c>
       <c r="D99" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F99" t="s">
         <v>23</v>
@@ -3118,10 +3139,10 @@
         <v>10</v>
       </c>
       <c r="H99" s="2">
-        <v>7.3148148148148148E-3</v>
+        <v>7.858796296296296E-3</v>
       </c>
       <c r="I99" s="1">
-        <v>46237.8125</v>
+        <v>46237.813194444447</v>
       </c>
       <c r="J99" s="2">
         <v>0</v>
@@ -3135,10 +3156,10 @@
         <v>26</v>
       </c>
       <c r="C100">
-        <v>5167</v>
+        <v>5164</v>
       </c>
       <c r="D100" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F100" t="s">
         <v>23</v>
@@ -3147,10 +3168,10 @@
         <v>10</v>
       </c>
       <c r="H100" s="2">
-        <v>7.858796296296296E-3</v>
+        <v>7.4074074074074077E-3</v>
       </c>
       <c r="I100" s="1">
-        <v>46237.813194444447</v>
+        <v>46237.813888888886</v>
       </c>
       <c r="J100" s="2">
         <v>0</v>
@@ -3164,25 +3185,25 @@
         <v>26</v>
       </c>
       <c r="C101">
-        <v>5164</v>
+        <v>5937</v>
       </c>
       <c r="D101" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F101" t="s">
         <v>23</v>
       </c>
       <c r="G101" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H101" s="2">
-        <v>7.4074074074074077E-3</v>
+        <v>0</v>
       </c>
       <c r="I101" s="1">
         <v>46237.813888888886</v>
       </c>
       <c r="J101" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K101" s="1" t="s">
         <v>11</v>
@@ -3193,22 +3214,22 @@
         <v>26</v>
       </c>
       <c r="C102">
-        <v>5937</v>
+        <v>5936</v>
       </c>
       <c r="D102" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F102" t="s">
         <v>23</v>
       </c>
       <c r="G102" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H102" s="2">
-        <v>0</v>
+        <v>8.0439814814814818E-3</v>
       </c>
       <c r="I102" s="1">
-        <v>46237.813888888886</v>
+        <v>46237.814583333333</v>
       </c>
       <c r="J102" s="2">
         <v>0</v>
@@ -3218,33 +3239,10 @@
       </c>
     </row>
     <row r="103" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B103" t="s">
-        <v>26</v>
-      </c>
-      <c r="C103">
-        <v>5936</v>
-      </c>
-      <c r="D103" t="s">
-        <v>40</v>
-      </c>
-      <c r="F103" t="s">
-        <v>23</v>
-      </c>
-      <c r="G103" t="s">
-        <v>10</v>
-      </c>
-      <c r="H103" s="2">
-        <v>8.0439814814814818E-3</v>
-      </c>
-      <c r="I103" s="1">
-        <v>46237.814583333333</v>
-      </c>
-      <c r="J103" s="2">
-        <v>0</v>
-      </c>
-      <c r="K103" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="H103" s="2"/>
+      <c r="I103" s="1"/>
+      <c r="J103" s="2"/>
+      <c r="K103" s="1"/>
     </row>
     <row r="104" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H104" s="2"/>
@@ -3294,7 +3292,7 @@
       <c r="J111" s="2"/>
       <c r="K111" s="1"/>
     </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H112" s="2"/>
       <c r="I112" s="1"/>
       <c r="J112" s="2"/>
@@ -3312,7 +3310,7 @@
       <c r="J114" s="2"/>
       <c r="K114" s="1"/>
     </row>
-    <row r="115" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H115" s="2"/>
       <c r="I115" s="1"/>
       <c r="J115" s="2"/>
@@ -3384,7 +3382,7 @@
       <c r="J126" s="2"/>
       <c r="K126" s="1"/>
     </row>
-    <row r="127" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H127" s="2"/>
       <c r="I127" s="1"/>
       <c r="J127" s="2"/>
@@ -3666,7 +3664,7 @@
       <c r="J173" s="2"/>
       <c r="K173" s="1"/>
     </row>
-    <row r="174" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H174" s="2"/>
       <c r="I174" s="1"/>
       <c r="J174" s="2"/>
@@ -3696,7 +3694,7 @@
       <c r="J178" s="2"/>
       <c r="K178" s="1"/>
     </row>
-    <row r="179" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="179" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H179" s="2"/>
       <c r="I179" s="1"/>
       <c r="J179" s="2"/>
@@ -3756,7 +3754,7 @@
       <c r="J188" s="2"/>
       <c r="K188" s="1"/>
     </row>
-    <row r="189" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H189" s="2"/>
       <c r="I189" s="1"/>
       <c r="J189" s="2"/>
@@ -3864,7 +3862,7 @@
       <c r="J206" s="2"/>
       <c r="K206" s="1"/>
     </row>
-    <row r="207" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="207" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H207" s="2"/>
       <c r="I207" s="1"/>
       <c r="J207" s="2"/>
@@ -4056,7 +4054,7 @@
       <c r="J238" s="2"/>
       <c r="K238" s="1"/>
     </row>
-    <row r="239" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="239" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H239" s="2"/>
       <c r="I239" s="1"/>
       <c r="J239" s="2"/>
@@ -4572,7 +4570,7 @@
       <c r="J324" s="2"/>
       <c r="K324" s="1"/>
     </row>
-    <row r="325" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="325" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H325" s="2"/>
       <c r="I325" s="1"/>
       <c r="J325" s="2"/>
@@ -4638,7 +4636,7 @@
       <c r="J335" s="2"/>
       <c r="K335" s="1"/>
     </row>
-    <row r="336" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="336" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H336" s="2"/>
       <c r="I336" s="1"/>
       <c r="J336" s="2"/>
@@ -4650,7 +4648,7 @@
       <c r="J337" s="2"/>
       <c r="K337" s="1"/>
     </row>
-    <row r="338" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="338" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H338" s="2"/>
       <c r="I338" s="1"/>
       <c r="J338" s="2"/>
@@ -4746,7 +4744,7 @@
       <c r="J353" s="2"/>
       <c r="K353" s="1"/>
     </row>
-    <row r="354" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="354" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H354" s="2"/>
       <c r="I354" s="1"/>
       <c r="J354" s="2"/>
@@ -4758,7 +4756,7 @@
       <c r="J355" s="2"/>
       <c r="K355" s="1"/>
     </row>
-    <row r="356" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="356" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H356" s="2"/>
       <c r="I356" s="1"/>
       <c r="J356" s="2"/>
@@ -4854,7 +4852,7 @@
       <c r="J371" s="2"/>
       <c r="K371" s="1"/>
     </row>
-    <row r="372" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="372" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H372" s="2"/>
       <c r="I372" s="1"/>
       <c r="J372" s="2"/>
@@ -4914,7 +4912,7 @@
       <c r="J381" s="2"/>
       <c r="K381" s="1"/>
     </row>
-    <row r="382" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="382" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H382" s="2"/>
       <c r="I382" s="1"/>
       <c r="J382" s="2"/>
@@ -43867,6 +43865,7 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -44159,6 +44158,8 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7055" s="2"/>
+      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -44469,6 +44470,7 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -44593,6 +44595,7 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -44604,6 +44607,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -44752,6 +44756,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
@@ -44762,10 +44767,12 @@
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
@@ -44799,15 +44806,18 @@
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
@@ -44848,18 +44858,22 @@
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -44875,6 +44889,7 @@
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
@@ -44884,10 +44899,12 @@
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
@@ -44923,10 +44940,12 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
@@ -44952,6 +44971,7 @@
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
@@ -44966,6 +44986,7 @@
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -45000,6 +45021,7 @@
       <c r="K7205" s="1"/>
     </row>
     <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7206" s="2"/>
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
@@ -45009,6 +45031,7 @@
       <c r="K7207" s="1"/>
     </row>
     <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7208" s="2"/>
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
@@ -45018,6 +45041,7 @@
       <c r="K7209" s="1"/>
     </row>
     <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7210" s="2"/>
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
@@ -45032,15 +45056,16 @@
       <c r="K7212" s="1"/>
     </row>
     <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
     <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7214" s="2"/>
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
     <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7215" s="2"/>
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
@@ -45070,6 +45095,7 @@
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -45090,11 +45116,13 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7225" s="2"/>
       <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
@@ -45103,6 +45131,7 @@
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
@@ -45132,6 +45161,7 @@
       <c r="K7233" s="1"/>
     </row>
     <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7234" s="2"/>
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
@@ -45141,10 +45171,12 @@
       <c r="K7235" s="1"/>
     </row>
     <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7236" s="2"/>
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
     <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7237" s="2"/>
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
@@ -45159,14 +45191,17 @@
       <c r="K7239" s="1"/>
     </row>
     <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7240" s="2"/>
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
     <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7241" s="2"/>
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
     <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7242" s="2"/>
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
@@ -45186,10 +45221,12 @@
       <c r="K7245" s="1"/>
     </row>
     <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7246" s="2"/>
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
     <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7247" s="2"/>
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
@@ -45209,9 +45246,12 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7251" s="2"/>
+      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
@@ -45246,18 +45286,22 @@
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -45272,12 +45316,12 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
@@ -45292,10 +45336,12 @@
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
@@ -45315,6 +45361,7 @@
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
@@ -45334,6 +45381,7 @@
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -45343,6 +45391,7 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
@@ -45388,6 +45437,7 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
@@ -45397,6 +45447,7 @@
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
@@ -45411,6 +45462,7 @@
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
@@ -45420,10 +45472,12 @@
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
@@ -45438,6 +45492,7 @@
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
@@ -45447,6 +45502,7 @@
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
@@ -45466,6 +45522,7 @@
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
@@ -45485,10 +45542,12 @@
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -45498,6 +45557,7 @@
       <c r="K7312" s="1"/>
     </row>
     <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7313" s="2"/>
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
@@ -45508,10 +45568,12 @@
       <c r="K7314" s="1"/>
     </row>
     <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7315" s="2"/>
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
     <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7316" s="2"/>
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
@@ -45526,18 +45588,22 @@
       <c r="K7318" s="1"/>
     </row>
     <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7319" s="2"/>
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
     <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7320" s="2"/>
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
     <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7321" s="2"/>
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
     <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7322" s="2"/>
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
@@ -45557,10 +45623,12 @@
       <c r="K7325" s="1"/>
     </row>
     <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7326" s="2"/>
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
     <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7327" s="2"/>
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
@@ -45580,6 +45648,7 @@
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -45610,7 +45679,6 @@
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
@@ -45625,10 +45693,12 @@
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
@@ -45643,6 +45713,7 @@
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
@@ -45657,11 +45728,11 @@
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -45671,6 +45742,7 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
@@ -45686,6 +45758,7 @@
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
@@ -45700,6 +45773,7 @@
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -45720,6 +45794,7 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
@@ -45745,11 +45820,13 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
@@ -45768,15 +45845,16 @@
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
@@ -45786,6 +45864,7 @@
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
@@ -45805,6 +45884,7 @@
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
@@ -45819,6 +45899,7 @@
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
@@ -45838,10 +45919,12 @@
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -45851,6 +45934,7 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
@@ -45861,6 +45945,7 @@
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
@@ -45897,7 +45982,6 @@
       <c r="I7397" s="1"/>
     </row>
     <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
     <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
@@ -45906,6 +45990,7 @@
       <c r="K7399" s="1"/>
     </row>
     <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7400" s="2"/>
       <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
     </row>
@@ -45919,10 +46004,6 @@
     </row>
     <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7403" s="1"/>
-    </row>
-    <row r="7404" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7404" s="2"/>
-      <c r="I7404" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Indigo-Construction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E83318DA-70A4-4519-BD6C-903BE05D1760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E52616A-1DFF-4EF5-91A5-8EAFF1FB0ACB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -535,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7403"/>
+  <dimension ref="A1:K7400"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -611,7 +611,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H3" s="2"/>
       <c r="I3" s="1"/>
       <c r="J3" s="2"/>
@@ -764,7 +764,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>26</v>
       </c>
@@ -880,7 +880,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>26</v>
       </c>
@@ -1194,7 +1194,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>26</v>
       </c>
@@ -1368,7 +1368,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>26</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>26</v>
       </c>
@@ -1943,7 +1943,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>26</v>
       </c>
@@ -2460,7 +2460,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>26</v>
       </c>
@@ -2692,7 +2692,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H82" s="2"/>
       <c r="I82" s="1"/>
       <c r="J82" s="2"/>
@@ -2940,7 +2940,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>26</v>
       </c>
@@ -3292,7 +3292,7 @@
       <c r="J111" s="2"/>
       <c r="K111" s="1"/>
     </row>
-    <row r="112" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H112" s="2"/>
       <c r="I112" s="1"/>
       <c r="J112" s="2"/>
@@ -3310,7 +3310,7 @@
       <c r="J114" s="2"/>
       <c r="K114" s="1"/>
     </row>
-    <row r="115" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H115" s="2"/>
       <c r="I115" s="1"/>
       <c r="J115" s="2"/>
@@ -3382,7 +3382,7 @@
       <c r="J126" s="2"/>
       <c r="K126" s="1"/>
     </row>
-    <row r="127" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H127" s="2"/>
       <c r="I127" s="1"/>
       <c r="J127" s="2"/>
@@ -3664,7 +3664,7 @@
       <c r="J173" s="2"/>
       <c r="K173" s="1"/>
     </row>
-    <row r="174" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H174" s="2"/>
       <c r="I174" s="1"/>
       <c r="J174" s="2"/>
@@ -3694,7 +3694,7 @@
       <c r="J178" s="2"/>
       <c r="K178" s="1"/>
     </row>
-    <row r="179" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H179" s="2"/>
       <c r="I179" s="1"/>
       <c r="J179" s="2"/>
@@ -3754,7 +3754,7 @@
       <c r="J188" s="2"/>
       <c r="K188" s="1"/>
     </row>
-    <row r="189" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H189" s="2"/>
       <c r="I189" s="1"/>
       <c r="J189" s="2"/>
@@ -3862,7 +3862,7 @@
       <c r="J206" s="2"/>
       <c r="K206" s="1"/>
     </row>
-    <row r="207" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H207" s="2"/>
       <c r="I207" s="1"/>
       <c r="J207" s="2"/>
@@ -4054,7 +4054,7 @@
       <c r="J238" s="2"/>
       <c r="K238" s="1"/>
     </row>
-    <row r="239" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H239" s="2"/>
       <c r="I239" s="1"/>
       <c r="J239" s="2"/>
@@ -4570,7 +4570,7 @@
       <c r="J324" s="2"/>
       <c r="K324" s="1"/>
     </row>
-    <row r="325" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H325" s="2"/>
       <c r="I325" s="1"/>
       <c r="J325" s="2"/>
@@ -4636,7 +4636,7 @@
       <c r="J335" s="2"/>
       <c r="K335" s="1"/>
     </row>
-    <row r="336" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H336" s="2"/>
       <c r="I336" s="1"/>
       <c r="J336" s="2"/>
@@ -4648,7 +4648,7 @@
       <c r="J337" s="2"/>
       <c r="K337" s="1"/>
     </row>
-    <row r="338" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H338" s="2"/>
       <c r="I338" s="1"/>
       <c r="J338" s="2"/>
@@ -4744,7 +4744,7 @@
       <c r="J353" s="2"/>
       <c r="K353" s="1"/>
     </row>
-    <row r="354" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H354" s="2"/>
       <c r="I354" s="1"/>
       <c r="J354" s="2"/>
@@ -4756,7 +4756,7 @@
       <c r="J355" s="2"/>
       <c r="K355" s="1"/>
     </row>
-    <row r="356" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H356" s="2"/>
       <c r="I356" s="1"/>
       <c r="J356" s="2"/>
@@ -4852,7 +4852,7 @@
       <c r="J371" s="2"/>
       <c r="K371" s="1"/>
     </row>
-    <row r="372" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H372" s="2"/>
       <c r="I372" s="1"/>
       <c r="J372" s="2"/>
@@ -4912,7 +4912,7 @@
       <c r="J381" s="2"/>
       <c r="K381" s="1"/>
     </row>
-    <row r="382" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H382" s="2"/>
       <c r="I382" s="1"/>
       <c r="J382" s="2"/>
@@ -43865,7 +43865,6 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -44158,8 +44157,6 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7055" s="2"/>
-      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -44470,7 +44467,6 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -44595,7 +44591,6 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -44607,7 +44602,6 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -44756,35 +44750,29 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -44795,44 +44783,35 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7162" s="2"/>
-      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -44843,37 +44822,30 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -44884,52 +44856,42 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -44940,17 +44902,14 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -44961,32 +44920,26 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -44996,106 +44949,86 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7201" s="2"/>
+    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7202" s="2"/>
+    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7203" s="2"/>
+    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7204" s="2"/>
+    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7205" s="2"/>
+    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7206" s="2"/>
+    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7207" s="2"/>
+    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7208" s="2"/>
+    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7209" s="2"/>
+    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7210" s="2"/>
+    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7211" s="2"/>
+    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7212" s="2"/>
+    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7214" s="2"/>
+    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7215" s="2"/>
+    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7216" s="2"/>
+    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -45105,7 +45038,6 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -45116,127 +45048,101 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7225" s="2"/>
-      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7233" s="2"/>
+    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7234" s="2"/>
+    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7235" s="2"/>
+    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7236" s="2"/>
+    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7237" s="2"/>
+    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7238" s="2"/>
+    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7239" s="2"/>
+    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7240" s="2"/>
+    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7241" s="2"/>
+    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7242" s="2"/>
+    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7243" s="2"/>
+    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7244" s="2"/>
+    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7245" s="2"/>
+    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7246" s="2"/>
+    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7247" s="2"/>
+    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7248" s="2"/>
+    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -45246,62 +45152,49 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7251" s="2"/>
-      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -45321,67 +45214,54 @@
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -45391,38 +45271,31 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -45437,117 +45310,94 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -45556,99 +45406,80 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7313" s="2"/>
+    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7314" s="2"/>
+    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7315" s="2"/>
+    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7316" s="2"/>
+    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7317" s="2"/>
+    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7318" s="2"/>
+    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7319" s="2"/>
+    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7320" s="2"/>
+    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7321" s="2"/>
+    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7322" s="2"/>
+    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7323" s="2"/>
+    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7324" s="2"/>
+    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7325" s="2"/>
+    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7326" s="2"/>
+    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7327" s="2"/>
+    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7328" s="2"/>
+    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -45658,23 +45489,19 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
@@ -45683,52 +45510,42 @@
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
@@ -45742,38 +45559,31 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -45783,7 +45593,6 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -45794,23 +45603,19 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -45820,37 +45625,30 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
@@ -45859,72 +45657,58 @@
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -45934,76 +45718,51 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7393" s="2"/>
+    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7394" s="1"/>
+    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7395" s="2"/>
+    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7396" s="2"/>
+    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7397" s="2"/>
+    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7399" s="2"/>
-      <c r="I7399" s="1"/>
+    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7400" s="2"/>
-      <c r="I7400" s="1"/>
+    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7400" s="1"/>
-    </row>
-    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7401" s="2"/>
-      <c r="I7401" s="1"/>
-    </row>
-    <row r="7402" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7402" s="2"/>
-      <c r="I7402" s="1"/>
-    </row>
-    <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7403" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
